--- a/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>MFG</t>
   </si>
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>22501600</v>
+        <v>22840500</v>
       </c>
       <c r="E8" s="3">
-        <v>9587800</v>
+        <v>9732200</v>
       </c>
       <c r="F8" s="3">
-        <v>9671500</v>
+        <v>9817200</v>
       </c>
       <c r="G8" s="3">
-        <v>14283800</v>
+        <v>14498900</v>
       </c>
       <c r="H8" s="3">
-        <v>14657400</v>
+        <v>14878200</v>
       </c>
       <c r="I8" s="3">
-        <v>11698900</v>
+        <v>11875100</v>
       </c>
       <c r="J8" s="3">
-        <v>10020000</v>
+        <v>10170900</v>
       </c>
       <c r="K8" s="3">
         <v>10816200</v>
@@ -993,16 +993,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-51200</v>
+        <v>-51900</v>
       </c>
       <c r="E15" s="3">
-        <v>-52900</v>
+        <v>-53700</v>
       </c>
       <c r="F15" s="3">
-        <v>-56500</v>
+        <v>-57400</v>
       </c>
       <c r="G15" s="3">
-        <v>-61500</v>
+        <v>-62500</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>5</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15141800</v>
+        <v>15369900</v>
       </c>
       <c r="E17" s="3">
-        <v>3809500</v>
+        <v>3866900</v>
       </c>
       <c r="F17" s="3">
-        <v>3975500</v>
+        <v>4035400</v>
       </c>
       <c r="G17" s="3">
-        <v>9607000</v>
+        <v>9751700</v>
       </c>
       <c r="H17" s="3">
-        <v>8877500</v>
+        <v>9011200</v>
       </c>
       <c r="I17" s="3">
-        <v>4869300</v>
+        <v>4942600</v>
       </c>
       <c r="J17" s="3">
-        <v>4374700</v>
+        <v>4440600</v>
       </c>
       <c r="K17" s="3">
         <v>3702500</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7359700</v>
+        <v>7470600</v>
       </c>
       <c r="E18" s="3">
-        <v>5778300</v>
+        <v>5865300</v>
       </c>
       <c r="F18" s="3">
-        <v>5696000</v>
+        <v>5781800</v>
       </c>
       <c r="G18" s="3">
-        <v>4676700</v>
+        <v>4747200</v>
       </c>
       <c r="H18" s="3">
-        <v>5780000</v>
+        <v>5867000</v>
       </c>
       <c r="I18" s="3">
-        <v>6829600</v>
+        <v>6932500</v>
       </c>
       <c r="J18" s="3">
-        <v>5645200</v>
+        <v>5730300</v>
       </c>
       <c r="K18" s="3">
         <v>7113800</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-6900400</v>
+        <v>-7004400</v>
       </c>
       <c r="E20" s="3">
-        <v>-7388400</v>
+        <v>-7499700</v>
       </c>
       <c r="F20" s="3">
-        <v>1135000</v>
+        <v>1152100</v>
       </c>
       <c r="G20" s="3">
-        <v>-3657600</v>
+        <v>-3712700</v>
       </c>
       <c r="H20" s="3">
-        <v>-5215200</v>
+        <v>-5293700</v>
       </c>
       <c r="I20" s="3">
-        <v>-1256700</v>
+        <v>-1275600</v>
       </c>
       <c r="J20" s="3">
-        <v>-2455500</v>
+        <v>-2492500</v>
       </c>
       <c r="K20" s="3">
         <v>1513800</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2039100</v>
+        <v>2084200</v>
       </c>
       <c r="E21" s="3">
-        <v>-100400</v>
+        <v>-88100</v>
       </c>
       <c r="F21" s="3">
-        <v>8362400</v>
+        <v>8502300</v>
       </c>
       <c r="G21" s="3">
-        <v>2630200</v>
+        <v>2684500</v>
       </c>
       <c r="H21" s="3">
-        <v>2912400</v>
+        <v>2977800</v>
       </c>
       <c r="I21" s="3">
-        <v>6757200</v>
+        <v>6869800</v>
       </c>
       <c r="J21" s="3">
-        <v>4321300</v>
+        <v>4396800</v>
       </c>
       <c r="K21" s="3">
         <v>9846700</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>459300</v>
+        <v>466200</v>
       </c>
       <c r="E23" s="3">
-        <v>-1610100</v>
+        <v>-1634400</v>
       </c>
       <c r="F23" s="3">
-        <v>6831000</v>
+        <v>6933900</v>
       </c>
       <c r="G23" s="3">
-        <v>1019200</v>
+        <v>1034500</v>
       </c>
       <c r="H23" s="3">
-        <v>564800</v>
+        <v>573300</v>
       </c>
       <c r="I23" s="3">
-        <v>5572900</v>
+        <v>5656900</v>
       </c>
       <c r="J23" s="3">
-        <v>3189700</v>
+        <v>3237700</v>
       </c>
       <c r="K23" s="3">
         <v>8627500</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>233300</v>
+        <v>236900</v>
       </c>
       <c r="E24" s="3">
-        <v>-936400</v>
+        <v>-950500</v>
       </c>
       <c r="F24" s="3">
-        <v>1399200</v>
+        <v>1420200</v>
       </c>
       <c r="G24" s="3">
-        <v>313200</v>
+        <v>318000</v>
       </c>
       <c r="H24" s="3">
-        <v>62000</v>
+        <v>62900</v>
       </c>
       <c r="I24" s="3">
-        <v>1577700</v>
+        <v>1601500</v>
       </c>
       <c r="J24" s="3">
-        <v>605900</v>
+        <v>615000</v>
       </c>
       <c r="K24" s="3">
         <v>2498600</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>225900</v>
+        <v>229300</v>
       </c>
       <c r="E26" s="3">
-        <v>-673800</v>
+        <v>-683900</v>
       </c>
       <c r="F26" s="3">
-        <v>5431800</v>
+        <v>5513600</v>
       </c>
       <c r="G26" s="3">
-        <v>705900</v>
+        <v>716600</v>
       </c>
       <c r="H26" s="3">
-        <v>502800</v>
+        <v>510400</v>
       </c>
       <c r="I26" s="3">
-        <v>3995200</v>
+        <v>4055400</v>
       </c>
       <c r="J26" s="3">
-        <v>2583800</v>
+        <v>2622700</v>
       </c>
       <c r="K26" s="3">
         <v>6129000</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-93000</v>
+        <v>-94400</v>
       </c>
       <c r="E27" s="3">
-        <v>-695400</v>
+        <v>-705800</v>
       </c>
       <c r="F27" s="3">
-        <v>3862900</v>
+        <v>3921100</v>
       </c>
       <c r="G27" s="3">
-        <v>997300</v>
+        <v>1012300</v>
       </c>
       <c r="H27" s="3">
-        <v>560900</v>
+        <v>569300</v>
       </c>
       <c r="I27" s="3">
-        <v>3835300</v>
+        <v>3893100</v>
       </c>
       <c r="J27" s="3">
-        <v>2406600</v>
+        <v>2442800</v>
       </c>
       <c r="K27" s="3">
         <v>6114500</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>6900400</v>
+        <v>7004400</v>
       </c>
       <c r="E32" s="3">
-        <v>7388400</v>
+        <v>7499700</v>
       </c>
       <c r="F32" s="3">
-        <v>-1135000</v>
+        <v>-1152100</v>
       </c>
       <c r="G32" s="3">
-        <v>3657600</v>
+        <v>3712700</v>
       </c>
       <c r="H32" s="3">
-        <v>5215200</v>
+        <v>5293700</v>
       </c>
       <c r="I32" s="3">
-        <v>1256700</v>
+        <v>1275600</v>
       </c>
       <c r="J32" s="3">
-        <v>2455500</v>
+        <v>2492500</v>
       </c>
       <c r="K32" s="3">
         <v>-1513800</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-93000</v>
+        <v>-94400</v>
       </c>
       <c r="E33" s="3">
-        <v>-695400</v>
+        <v>-705800</v>
       </c>
       <c r="F33" s="3">
-        <v>3862900</v>
+        <v>3921100</v>
       </c>
       <c r="G33" s="3">
-        <v>997300</v>
+        <v>1012300</v>
       </c>
       <c r="H33" s="3">
-        <v>560900</v>
+        <v>569300</v>
       </c>
       <c r="I33" s="3">
-        <v>3835300</v>
+        <v>3893100</v>
       </c>
       <c r="J33" s="3">
-        <v>2406600</v>
+        <v>2442800</v>
       </c>
       <c r="K33" s="3">
         <v>6114500</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-93000</v>
+        <v>-94400</v>
       </c>
       <c r="E35" s="3">
-        <v>-695400</v>
+        <v>-705800</v>
       </c>
       <c r="F35" s="3">
-        <v>3862900</v>
+        <v>3921100</v>
       </c>
       <c r="G35" s="3">
-        <v>997300</v>
+        <v>1012300</v>
       </c>
       <c r="H35" s="3">
-        <v>560900</v>
+        <v>569300</v>
       </c>
       <c r="I35" s="3">
-        <v>3835300</v>
+        <v>3893100</v>
       </c>
       <c r="J35" s="3">
-        <v>2406600</v>
+        <v>2442800</v>
       </c>
       <c r="K35" s="3">
         <v>6114500</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>451469000</v>
+        <v>458268000</v>
       </c>
       <c r="E41" s="3">
-        <v>346437000</v>
+        <v>351655000</v>
       </c>
       <c r="F41" s="3">
-        <v>323594000</v>
+        <v>328468000</v>
       </c>
       <c r="G41" s="3">
-        <v>278555000</v>
+        <v>282751000</v>
       </c>
       <c r="H41" s="3">
-        <v>303267000</v>
+        <v>307834000</v>
       </c>
       <c r="I41" s="3">
-        <v>319855000</v>
+        <v>324672000</v>
       </c>
       <c r="J41" s="3">
-        <v>315978000</v>
+        <v>320736000</v>
       </c>
       <c r="K41" s="3">
         <v>264247000</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>333297000</v>
+        <v>338317000</v>
       </c>
       <c r="E42" s="3">
-        <v>298422000</v>
+        <v>302916000</v>
       </c>
       <c r="F42" s="3">
-        <v>299346000</v>
+        <v>303854000</v>
       </c>
       <c r="G42" s="3">
-        <v>343462000</v>
+        <v>348635000</v>
       </c>
       <c r="H42" s="3">
-        <v>261775000</v>
+        <v>265718000</v>
       </c>
       <c r="I42" s="3">
-        <v>264401000</v>
+        <v>268383000</v>
       </c>
       <c r="J42" s="3">
-        <v>270846000</v>
+        <v>274925000</v>
       </c>
       <c r="K42" s="3">
         <v>322177000</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14631600</v>
+        <v>14852000</v>
       </c>
       <c r="E48" s="3">
-        <v>15100900</v>
+        <v>15328400</v>
       </c>
       <c r="F48" s="3">
-        <v>16088700</v>
+        <v>16331000</v>
       </c>
       <c r="G48" s="3">
-        <v>16396300</v>
+        <v>16643200</v>
       </c>
       <c r="H48" s="3">
-        <v>12622300</v>
+        <v>12812400</v>
       </c>
       <c r="I48" s="3">
-        <v>14051500</v>
+        <v>14263100</v>
       </c>
       <c r="J48" s="3">
-        <v>13554100</v>
+        <v>13758200</v>
       </c>
       <c r="K48" s="3">
         <v>13251900</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>913700</v>
+        <v>927500</v>
       </c>
       <c r="E49" s="3">
-        <v>933800</v>
+        <v>947900</v>
       </c>
       <c r="F49" s="3">
-        <v>988100</v>
+        <v>1003000</v>
       </c>
       <c r="G49" s="3">
-        <v>1047000</v>
+        <v>1062800</v>
       </c>
       <c r="H49" s="3">
-        <v>1124800</v>
+        <v>1141700</v>
       </c>
       <c r="I49" s="3">
-        <v>1192700</v>
+        <v>1210700</v>
       </c>
       <c r="J49" s="3">
-        <v>1257100</v>
+        <v>1276000</v>
       </c>
       <c r="K49" s="3">
         <v>488500</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2567000</v>
+        <v>2605600</v>
       </c>
       <c r="E52" s="3">
-        <v>1841400</v>
+        <v>1869100</v>
       </c>
       <c r="F52" s="3">
-        <v>298600</v>
+        <v>303100</v>
       </c>
       <c r="G52" s="3">
-        <v>907800</v>
+        <v>921400</v>
       </c>
       <c r="H52" s="3">
-        <v>330500</v>
+        <v>335500</v>
       </c>
       <c r="I52" s="3">
-        <v>379100</v>
+        <v>384800</v>
       </c>
       <c r="J52" s="3">
-        <v>421800</v>
+        <v>428100</v>
       </c>
       <c r="K52" s="3">
         <v>413500</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1651900000</v>
+        <v>1676780000</v>
       </c>
       <c r="E54" s="3">
-        <v>1537500000</v>
+        <v>1560650000</v>
       </c>
       <c r="F54" s="3">
-        <v>1471770000</v>
+        <v>1493930000</v>
       </c>
       <c r="G54" s="3">
-        <v>1402490000</v>
+        <v>1423610000</v>
       </c>
       <c r="H54" s="3">
-        <v>1312140000</v>
+        <v>1331900000</v>
       </c>
       <c r="I54" s="3">
-        <v>1356260000</v>
+        <v>1376680000</v>
       </c>
       <c r="J54" s="3">
-        <v>1331030000</v>
+        <v>1351080000</v>
       </c>
       <c r="K54" s="3">
         <v>1397370000</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15448700</v>
+        <v>15681300</v>
       </c>
       <c r="E57" s="3">
-        <v>12626000</v>
+        <v>12816100</v>
       </c>
       <c r="F57" s="3">
-        <v>19789800</v>
+        <v>20087800</v>
       </c>
       <c r="G57" s="3">
-        <v>16840400</v>
+        <v>17094000</v>
       </c>
       <c r="H57" s="3">
-        <v>20020200</v>
+        <v>20321700</v>
       </c>
       <c r="I57" s="3">
-        <v>12394100</v>
+        <v>12580700</v>
       </c>
       <c r="J57" s="3">
-        <v>12496100</v>
+        <v>12684300</v>
       </c>
       <c r="K57" s="3">
         <v>23974500</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>219637000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>206705000</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7317900</v>
+        <v>7428100</v>
       </c>
       <c r="E59" s="3">
-        <v>5706500</v>
+        <v>5792500</v>
       </c>
       <c r="F59" s="3">
-        <v>5893100</v>
+        <v>5981800</v>
       </c>
       <c r="G59" s="3">
-        <v>6275800</v>
+        <v>6370300</v>
       </c>
       <c r="H59" s="3">
-        <v>2305700</v>
+        <v>2340400</v>
       </c>
       <c r="I59" s="3">
-        <v>1974600</v>
+        <v>2004400</v>
       </c>
       <c r="J59" s="3">
-        <v>1878500</v>
+        <v>1906800</v>
       </c>
       <c r="K59" s="3">
         <v>2005500</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>98889700</v>
+        <v>100366000</v>
       </c>
       <c r="E61" s="3">
-        <v>83519400</v>
+        <v>84757000</v>
       </c>
       <c r="F61" s="3">
-        <v>77731000</v>
+        <v>78901600</v>
       </c>
       <c r="G61" s="3">
-        <v>68698400</v>
+        <v>69733100</v>
       </c>
       <c r="H61" s="3">
-        <v>76555200</v>
+        <v>77708200</v>
       </c>
       <c r="I61" s="3">
-        <v>86022700</v>
+        <v>87318300</v>
       </c>
       <c r="J61" s="3">
-        <v>96475300</v>
+        <v>97928300</v>
       </c>
       <c r="K61" s="3">
         <v>106459000</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>168800</v>
+        <v>171400</v>
       </c>
       <c r="E62" s="3">
-        <v>192800</v>
+        <v>195700</v>
       </c>
       <c r="F62" s="3">
-        <v>511000</v>
+        <v>518700</v>
       </c>
       <c r="G62" s="3">
-        <v>171800</v>
+        <v>174400</v>
       </c>
       <c r="H62" s="3">
-        <v>717900</v>
+        <v>728700</v>
       </c>
       <c r="I62" s="3">
-        <v>2033200</v>
+        <v>2063800</v>
       </c>
       <c r="J62" s="3">
-        <v>932800</v>
+        <v>946800</v>
       </c>
       <c r="K62" s="3">
         <v>1455400</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1592710000</v>
+        <v>1616690000</v>
       </c>
       <c r="E66" s="3">
-        <v>1478310000</v>
+        <v>1500570000</v>
       </c>
       <c r="F66" s="3">
-        <v>1411310000</v>
+        <v>1432560000</v>
       </c>
       <c r="G66" s="3">
-        <v>1345970000</v>
+        <v>1366240000</v>
       </c>
       <c r="H66" s="3">
-        <v>1254190000</v>
+        <v>1273080000</v>
       </c>
       <c r="I66" s="3">
-        <v>1297370000</v>
+        <v>1316910000</v>
       </c>
       <c r="J66" s="3">
-        <v>1276170000</v>
+        <v>1295390000</v>
       </c>
       <c r="K66" s="3">
         <v>1339590000</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>16215900</v>
+        <v>16460100</v>
       </c>
       <c r="E72" s="3">
-        <v>17699600</v>
+        <v>17966200</v>
       </c>
       <c r="F72" s="3">
-        <v>19703400</v>
+        <v>20000200</v>
       </c>
       <c r="G72" s="3">
-        <v>17933100</v>
+        <v>18203200</v>
       </c>
       <c r="H72" s="3">
-        <v>18197200</v>
+        <v>18471300</v>
       </c>
       <c r="I72" s="3">
-        <v>8672800</v>
+        <v>8803400</v>
       </c>
       <c r="J72" s="3">
-        <v>6101500</v>
+        <v>6193300</v>
       </c>
       <c r="K72" s="3">
         <v>5384300</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>59198900</v>
+        <v>60090400</v>
       </c>
       <c r="E76" s="3">
-        <v>59190400</v>
+        <v>60081800</v>
       </c>
       <c r="F76" s="3">
-        <v>60458800</v>
+        <v>61369300</v>
       </c>
       <c r="G76" s="3">
-        <v>56522100</v>
+        <v>57373300</v>
       </c>
       <c r="H76" s="3">
-        <v>57944100</v>
+        <v>58816700</v>
       </c>
       <c r="I76" s="3">
-        <v>58886300</v>
+        <v>59773200</v>
       </c>
       <c r="J76" s="3">
-        <v>54855400</v>
+        <v>55681500</v>
       </c>
       <c r="K76" s="3">
         <v>57071700</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-93000</v>
+        <v>-94400</v>
       </c>
       <c r="E81" s="3">
-        <v>-695400</v>
+        <v>-705800</v>
       </c>
       <c r="F81" s="3">
-        <v>3862900</v>
+        <v>3921100</v>
       </c>
       <c r="G81" s="3">
-        <v>997300</v>
+        <v>1012300</v>
       </c>
       <c r="H81" s="3">
-        <v>560900</v>
+        <v>569300</v>
       </c>
       <c r="I81" s="3">
-        <v>3835300</v>
+        <v>3893100</v>
       </c>
       <c r="J81" s="3">
-        <v>2406600</v>
+        <v>2442800</v>
       </c>
       <c r="K81" s="3">
         <v>6114500</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1586900</v>
+        <v>1610800</v>
       </c>
       <c r="E83" s="3">
-        <v>1516600</v>
+        <v>1539400</v>
       </c>
       <c r="F83" s="3">
-        <v>1538300</v>
+        <v>1561500</v>
       </c>
       <c r="G83" s="3">
-        <v>1618300</v>
+        <v>1642700</v>
       </c>
       <c r="H83" s="3">
-        <v>2358300</v>
+        <v>2393800</v>
       </c>
       <c r="I83" s="3">
-        <v>1189600</v>
+        <v>1207500</v>
       </c>
       <c r="J83" s="3">
-        <v>1136800</v>
+        <v>1153900</v>
       </c>
       <c r="K83" s="3">
         <v>1210800</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>6685900</v>
+        <v>6786600</v>
       </c>
       <c r="E89" s="3">
-        <v>36507300</v>
+        <v>37057100</v>
       </c>
       <c r="F89" s="3">
-        <v>3112500</v>
+        <v>3159400</v>
       </c>
       <c r="G89" s="3">
-        <v>-26832700</v>
+        <v>-27236800</v>
       </c>
       <c r="H89" s="3">
-        <v>4389200</v>
+        <v>4455300</v>
       </c>
       <c r="I89" s="3">
-        <v>-1046900</v>
+        <v>-1062600</v>
       </c>
       <c r="J89" s="3">
-        <v>8056400</v>
+        <v>8177700</v>
       </c>
       <c r="K89" s="3">
         <v>1742700</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1232300</v>
+        <v>-1250800</v>
       </c>
       <c r="E91" s="3">
-        <v>-904600</v>
+        <v>-918200</v>
       </c>
       <c r="F91" s="3">
-        <v>-1404300</v>
+        <v>-1425500</v>
       </c>
       <c r="G91" s="3">
-        <v>-1613700</v>
+        <v>-1638000</v>
       </c>
       <c r="H91" s="3">
-        <v>-1047200</v>
+        <v>-1063000</v>
       </c>
       <c r="I91" s="3">
-        <v>-1940200</v>
+        <v>-1969400</v>
       </c>
       <c r="J91" s="3">
-        <v>-2861300</v>
+        <v>-2904400</v>
       </c>
       <c r="K91" s="3">
         <v>-2801600</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>41104800</v>
+        <v>41723900</v>
       </c>
       <c r="E94" s="3">
-        <v>-33307100</v>
+        <v>-33808700</v>
       </c>
       <c r="F94" s="3">
-        <v>-17352300</v>
+        <v>-17613600</v>
       </c>
       <c r="G94" s="3">
-        <v>-78402400</v>
+        <v>-79583100</v>
       </c>
       <c r="H94" s="3">
-        <v>-44977800</v>
+        <v>-45655200</v>
       </c>
       <c r="I94" s="3">
-        <v>-29132800</v>
+        <v>-29571600</v>
       </c>
       <c r="J94" s="3">
-        <v>-85002400</v>
+        <v>-86282600</v>
       </c>
       <c r="K94" s="3">
         <v>-43101900</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1390800</v>
+        <v>-1411700</v>
       </c>
       <c r="E96" s="3">
-        <v>-1306600</v>
+        <v>-1326300</v>
       </c>
       <c r="F96" s="3">
-        <v>-1264900</v>
+        <v>-1284000</v>
       </c>
       <c r="G96" s="3">
-        <v>-1264200</v>
+        <v>-1283200</v>
       </c>
       <c r="H96" s="3">
-        <v>-1264300</v>
+        <v>-1283400</v>
       </c>
       <c r="I96" s="3">
-        <v>-1264100</v>
+        <v>-1283200</v>
       </c>
       <c r="J96" s="3">
-        <v>-1261800</v>
+        <v>-1280800</v>
       </c>
       <c r="K96" s="3">
         <v>-1408000</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>51545300</v>
+        <v>52321600</v>
       </c>
       <c r="E100" s="3">
-        <v>13223100</v>
+        <v>13422300</v>
       </c>
       <c r="F100" s="3">
-        <v>57714300</v>
+        <v>58583500</v>
       </c>
       <c r="G100" s="3">
-        <v>82050200</v>
+        <v>83285900</v>
       </c>
       <c r="H100" s="3">
-        <v>22631700</v>
+        <v>22972500</v>
       </c>
       <c r="I100" s="3">
-        <v>30893400</v>
+        <v>31358700</v>
       </c>
       <c r="J100" s="3">
-        <v>78815200</v>
+        <v>80002100</v>
       </c>
       <c r="K100" s="3">
         <v>40078300</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>5695500</v>
+        <v>5781300</v>
       </c>
       <c r="E101" s="3">
-        <v>6419500</v>
+        <v>6516200</v>
       </c>
       <c r="F101" s="3">
-        <v>1564500</v>
+        <v>1588000</v>
       </c>
       <c r="G101" s="3">
-        <v>-1526700</v>
+        <v>-1549600</v>
       </c>
       <c r="H101" s="3">
-        <v>1369100</v>
+        <v>1389700</v>
       </c>
       <c r="I101" s="3">
-        <v>-91900</v>
+        <v>-93300</v>
       </c>
       <c r="J101" s="3">
-        <v>-79000</v>
+        <v>-80200</v>
       </c>
       <c r="K101" s="3">
         <v>-202300</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>105031600</v>
+        <v>106613400</v>
       </c>
       <c r="E102" s="3">
-        <v>22842900</v>
+        <v>23186900</v>
       </c>
       <c r="F102" s="3">
-        <v>45039000</v>
+        <v>45717300</v>
       </c>
       <c r="G102" s="3">
-        <v>-24711600</v>
+        <v>-25083800</v>
       </c>
       <c r="H102" s="3">
-        <v>-16587900</v>
+        <v>-16837700</v>
       </c>
       <c r="I102" s="3">
-        <v>621800</v>
+        <v>631200</v>
       </c>
       <c r="J102" s="3">
-        <v>1790100</v>
+        <v>1817100</v>
       </c>
       <c r="K102" s="3">
         <v>-1483200</v>

--- a/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>22840500</v>
+        <v>21620500</v>
       </c>
       <c r="E8" s="3">
-        <v>9732200</v>
+        <v>9212300</v>
       </c>
       <c r="F8" s="3">
-        <v>9817200</v>
+        <v>9292800</v>
       </c>
       <c r="G8" s="3">
-        <v>14498900</v>
+        <v>13724500</v>
       </c>
       <c r="H8" s="3">
-        <v>14878200</v>
+        <v>14083500</v>
       </c>
       <c r="I8" s="3">
-        <v>11875100</v>
+        <v>11240800</v>
       </c>
       <c r="J8" s="3">
-        <v>10170900</v>
+        <v>9627600</v>
       </c>
       <c r="K8" s="3">
         <v>10816200</v>
@@ -993,16 +993,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-51900</v>
+        <v>-49200</v>
       </c>
       <c r="E15" s="3">
-        <v>-53700</v>
+        <v>-50800</v>
       </c>
       <c r="F15" s="3">
-        <v>-57400</v>
+        <v>-54300</v>
       </c>
       <c r="G15" s="3">
-        <v>-62500</v>
+        <v>-59100</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>5</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15369900</v>
+        <v>14548900</v>
       </c>
       <c r="E17" s="3">
-        <v>3866900</v>
+        <v>3660300</v>
       </c>
       <c r="F17" s="3">
-        <v>4035400</v>
+        <v>3819800</v>
       </c>
       <c r="G17" s="3">
-        <v>9751700</v>
+        <v>9230900</v>
       </c>
       <c r="H17" s="3">
-        <v>9011200</v>
+        <v>8529800</v>
       </c>
       <c r="I17" s="3">
-        <v>4942600</v>
+        <v>4678600</v>
       </c>
       <c r="J17" s="3">
-        <v>4440600</v>
+        <v>4203400</v>
       </c>
       <c r="K17" s="3">
         <v>3702500</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7470600</v>
+        <v>7071500</v>
       </c>
       <c r="E18" s="3">
-        <v>5865300</v>
+        <v>5552000</v>
       </c>
       <c r="F18" s="3">
-        <v>5781800</v>
+        <v>5473000</v>
       </c>
       <c r="G18" s="3">
-        <v>4747200</v>
+        <v>4493600</v>
       </c>
       <c r="H18" s="3">
-        <v>5867000</v>
+        <v>5553600</v>
       </c>
       <c r="I18" s="3">
-        <v>6932500</v>
+        <v>6562200</v>
       </c>
       <c r="J18" s="3">
-        <v>5730300</v>
+        <v>5424200</v>
       </c>
       <c r="K18" s="3">
         <v>7113800</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-7004400</v>
+        <v>-6630200</v>
       </c>
       <c r="E20" s="3">
-        <v>-7499700</v>
+        <v>-7099100</v>
       </c>
       <c r="F20" s="3">
-        <v>1152100</v>
+        <v>1090500</v>
       </c>
       <c r="G20" s="3">
-        <v>-3712700</v>
+        <v>-3514400</v>
       </c>
       <c r="H20" s="3">
-        <v>-5293700</v>
+        <v>-5011000</v>
       </c>
       <c r="I20" s="3">
-        <v>-1275600</v>
+        <v>-1207500</v>
       </c>
       <c r="J20" s="3">
-        <v>-2492500</v>
+        <v>-2359400</v>
       </c>
       <c r="K20" s="3">
         <v>1513800</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2084200</v>
+        <v>1963700</v>
       </c>
       <c r="E21" s="3">
-        <v>-88100</v>
+        <v>-92200</v>
       </c>
       <c r="F21" s="3">
-        <v>8502300</v>
+        <v>8039300</v>
       </c>
       <c r="G21" s="3">
-        <v>2684500</v>
+        <v>2531800</v>
       </c>
       <c r="H21" s="3">
-        <v>2977800</v>
+        <v>2805100</v>
       </c>
       <c r="I21" s="3">
-        <v>6869800</v>
+        <v>6496000</v>
       </c>
       <c r="J21" s="3">
-        <v>4396800</v>
+        <v>4155300</v>
       </c>
       <c r="K21" s="3">
         <v>9846700</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>466200</v>
+        <v>441300</v>
       </c>
       <c r="E23" s="3">
-        <v>-1634400</v>
+        <v>-1547100</v>
       </c>
       <c r="F23" s="3">
-        <v>6933900</v>
+        <v>6563500</v>
       </c>
       <c r="G23" s="3">
-        <v>1034500</v>
+        <v>979300</v>
       </c>
       <c r="H23" s="3">
-        <v>573300</v>
+        <v>542700</v>
       </c>
       <c r="I23" s="3">
-        <v>5656900</v>
+        <v>5354700</v>
       </c>
       <c r="J23" s="3">
-        <v>3237700</v>
+        <v>3064800</v>
       </c>
       <c r="K23" s="3">
         <v>8627500</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>236900</v>
+        <v>224200</v>
       </c>
       <c r="E24" s="3">
-        <v>-950500</v>
+        <v>-899700</v>
       </c>
       <c r="F24" s="3">
-        <v>1420200</v>
+        <v>1344400</v>
       </c>
       <c r="G24" s="3">
-        <v>318000</v>
+        <v>301000</v>
       </c>
       <c r="H24" s="3">
-        <v>62900</v>
+        <v>59600</v>
       </c>
       <c r="I24" s="3">
-        <v>1601500</v>
+        <v>1515900</v>
       </c>
       <c r="J24" s="3">
-        <v>615000</v>
+        <v>582100</v>
       </c>
       <c r="K24" s="3">
         <v>2498600</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>229300</v>
+        <v>217100</v>
       </c>
       <c r="E26" s="3">
-        <v>-683900</v>
+        <v>-647400</v>
       </c>
       <c r="F26" s="3">
-        <v>5513600</v>
+        <v>5219100</v>
       </c>
       <c r="G26" s="3">
-        <v>716600</v>
+        <v>678300</v>
       </c>
       <c r="H26" s="3">
-        <v>510400</v>
+        <v>483100</v>
       </c>
       <c r="I26" s="3">
-        <v>4055400</v>
+        <v>3838800</v>
       </c>
       <c r="J26" s="3">
-        <v>2622700</v>
+        <v>2482700</v>
       </c>
       <c r="K26" s="3">
         <v>6129000</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-94400</v>
+        <v>-89400</v>
       </c>
       <c r="E27" s="3">
-        <v>-705800</v>
+        <v>-668100</v>
       </c>
       <c r="F27" s="3">
-        <v>3921100</v>
+        <v>3711700</v>
       </c>
       <c r="G27" s="3">
-        <v>1012300</v>
+        <v>958200</v>
       </c>
       <c r="H27" s="3">
-        <v>569300</v>
+        <v>538900</v>
       </c>
       <c r="I27" s="3">
-        <v>3893100</v>
+        <v>3685100</v>
       </c>
       <c r="J27" s="3">
-        <v>2442800</v>
+        <v>2312400</v>
       </c>
       <c r="K27" s="3">
         <v>6114500</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>7004400</v>
+        <v>6630200</v>
       </c>
       <c r="E32" s="3">
-        <v>7499700</v>
+        <v>7099100</v>
       </c>
       <c r="F32" s="3">
-        <v>-1152100</v>
+        <v>-1090500</v>
       </c>
       <c r="G32" s="3">
-        <v>3712700</v>
+        <v>3514400</v>
       </c>
       <c r="H32" s="3">
-        <v>5293700</v>
+        <v>5011000</v>
       </c>
       <c r="I32" s="3">
-        <v>1275600</v>
+        <v>1207500</v>
       </c>
       <c r="J32" s="3">
-        <v>2492500</v>
+        <v>2359400</v>
       </c>
       <c r="K32" s="3">
         <v>-1513800</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-94400</v>
+        <v>-89400</v>
       </c>
       <c r="E33" s="3">
-        <v>-705800</v>
+        <v>-668100</v>
       </c>
       <c r="F33" s="3">
-        <v>3921100</v>
+        <v>3711700</v>
       </c>
       <c r="G33" s="3">
-        <v>1012300</v>
+        <v>958200</v>
       </c>
       <c r="H33" s="3">
-        <v>569300</v>
+        <v>538900</v>
       </c>
       <c r="I33" s="3">
-        <v>3893100</v>
+        <v>3685100</v>
       </c>
       <c r="J33" s="3">
-        <v>2442800</v>
+        <v>2312400</v>
       </c>
       <c r="K33" s="3">
         <v>6114500</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-94400</v>
+        <v>-89400</v>
       </c>
       <c r="E35" s="3">
-        <v>-705800</v>
+        <v>-668100</v>
       </c>
       <c r="F35" s="3">
-        <v>3921100</v>
+        <v>3711700</v>
       </c>
       <c r="G35" s="3">
-        <v>1012300</v>
+        <v>958200</v>
       </c>
       <c r="H35" s="3">
-        <v>569300</v>
+        <v>538900</v>
       </c>
       <c r="I35" s="3">
-        <v>3893100</v>
+        <v>3685100</v>
       </c>
       <c r="J35" s="3">
-        <v>2442800</v>
+        <v>2312400</v>
       </c>
       <c r="K35" s="3">
         <v>6114500</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>458268000</v>
+        <v>433791000</v>
       </c>
       <c r="E41" s="3">
-        <v>351655000</v>
+        <v>332872000</v>
       </c>
       <c r="F41" s="3">
-        <v>328468000</v>
+        <v>310924000</v>
       </c>
       <c r="G41" s="3">
-        <v>282751000</v>
+        <v>267648000</v>
       </c>
       <c r="H41" s="3">
-        <v>307834000</v>
+        <v>291392000</v>
       </c>
       <c r="I41" s="3">
-        <v>324672000</v>
+        <v>307331000</v>
       </c>
       <c r="J41" s="3">
-        <v>320736000</v>
+        <v>303605000</v>
       </c>
       <c r="K41" s="3">
         <v>264247000</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>338317000</v>
+        <v>320246000</v>
       </c>
       <c r="E42" s="3">
-        <v>302916000</v>
+        <v>286737000</v>
       </c>
       <c r="F42" s="3">
-        <v>303854000</v>
+        <v>287625000</v>
       </c>
       <c r="G42" s="3">
-        <v>348635000</v>
+        <v>330014000</v>
       </c>
       <c r="H42" s="3">
-        <v>265718000</v>
+        <v>251525000</v>
       </c>
       <c r="I42" s="3">
-        <v>268383000</v>
+        <v>254048000</v>
       </c>
       <c r="J42" s="3">
-        <v>274925000</v>
+        <v>260240000</v>
       </c>
       <c r="K42" s="3">
         <v>322177000</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14852000</v>
+        <v>14058700</v>
       </c>
       <c r="E48" s="3">
-        <v>15328400</v>
+        <v>14509600</v>
       </c>
       <c r="F48" s="3">
-        <v>16331000</v>
+        <v>15458700</v>
       </c>
       <c r="G48" s="3">
-        <v>16643200</v>
+        <v>15754200</v>
       </c>
       <c r="H48" s="3">
-        <v>12812400</v>
+        <v>12128100</v>
       </c>
       <c r="I48" s="3">
-        <v>14263100</v>
+        <v>13501300</v>
       </c>
       <c r="J48" s="3">
-        <v>13758200</v>
+        <v>13023300</v>
       </c>
       <c r="K48" s="3">
         <v>13251900</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>927500</v>
+        <v>877900</v>
       </c>
       <c r="E49" s="3">
-        <v>947900</v>
+        <v>897200</v>
       </c>
       <c r="F49" s="3">
-        <v>1003000</v>
+        <v>949400</v>
       </c>
       <c r="G49" s="3">
-        <v>1062800</v>
+        <v>1006000</v>
       </c>
       <c r="H49" s="3">
-        <v>1141700</v>
+        <v>1080700</v>
       </c>
       <c r="I49" s="3">
-        <v>1210700</v>
+        <v>1146000</v>
       </c>
       <c r="J49" s="3">
-        <v>1276000</v>
+        <v>1207900</v>
       </c>
       <c r="K49" s="3">
         <v>488500</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2605600</v>
+        <v>2466500</v>
       </c>
       <c r="E52" s="3">
-        <v>1869100</v>
+        <v>1769300</v>
       </c>
       <c r="F52" s="3">
-        <v>303100</v>
+        <v>286900</v>
       </c>
       <c r="G52" s="3">
-        <v>921400</v>
+        <v>872200</v>
       </c>
       <c r="H52" s="3">
-        <v>335500</v>
+        <v>317600</v>
       </c>
       <c r="I52" s="3">
-        <v>384800</v>
+        <v>364200</v>
       </c>
       <c r="J52" s="3">
-        <v>428100</v>
+        <v>405300</v>
       </c>
       <c r="K52" s="3">
         <v>413500</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1676780000</v>
+        <v>1587220000</v>
       </c>
       <c r="E54" s="3">
-        <v>1560650000</v>
+        <v>1477290000</v>
       </c>
       <c r="F54" s="3">
-        <v>1493930000</v>
+        <v>1414140000</v>
       </c>
       <c r="G54" s="3">
-        <v>1423610000</v>
+        <v>1347580000</v>
       </c>
       <c r="H54" s="3">
-        <v>1331900000</v>
+        <v>1260760000</v>
       </c>
       <c r="I54" s="3">
-        <v>1376680000</v>
+        <v>1303150000</v>
       </c>
       <c r="J54" s="3">
-        <v>1351080000</v>
+        <v>1278910000</v>
       </c>
       <c r="K54" s="3">
         <v>1397370000</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15681300</v>
+        <v>14843800</v>
       </c>
       <c r="E57" s="3">
-        <v>12816100</v>
+        <v>12131600</v>
       </c>
       <c r="F57" s="3">
-        <v>20087800</v>
+        <v>19014900</v>
       </c>
       <c r="G57" s="3">
-        <v>17094000</v>
+        <v>16181000</v>
       </c>
       <c r="H57" s="3">
-        <v>20321700</v>
+        <v>19236300</v>
       </c>
       <c r="I57" s="3">
-        <v>12580700</v>
+        <v>11908700</v>
       </c>
       <c r="J57" s="3">
-        <v>12684300</v>
+        <v>12006800</v>
       </c>
       <c r="K57" s="3">
         <v>23974500</v>
@@ -2573,10 +2573,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>219637000</v>
+        <v>207906000</v>
       </c>
       <c r="E58" s="3">
-        <v>206705000</v>
+        <v>195664000</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>5</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7428100</v>
+        <v>7031400</v>
       </c>
       <c r="E59" s="3">
-        <v>5792500</v>
+        <v>5483100</v>
       </c>
       <c r="F59" s="3">
-        <v>5981800</v>
+        <v>5662300</v>
       </c>
       <c r="G59" s="3">
-        <v>6370300</v>
+        <v>6030100</v>
       </c>
       <c r="H59" s="3">
-        <v>2340400</v>
+        <v>2215400</v>
       </c>
       <c r="I59" s="3">
-        <v>2004400</v>
+        <v>1897300</v>
       </c>
       <c r="J59" s="3">
-        <v>1906800</v>
+        <v>1804900</v>
       </c>
       <c r="K59" s="3">
         <v>2005500</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100366000</v>
+        <v>95004700</v>
       </c>
       <c r="E61" s="3">
-        <v>84757000</v>
+        <v>80229900</v>
       </c>
       <c r="F61" s="3">
-        <v>78901600</v>
+        <v>74687300</v>
       </c>
       <c r="G61" s="3">
-        <v>69733100</v>
+        <v>66008400</v>
       </c>
       <c r="H61" s="3">
-        <v>77708200</v>
+        <v>73557600</v>
       </c>
       <c r="I61" s="3">
-        <v>87318300</v>
+        <v>82654400</v>
       </c>
       <c r="J61" s="3">
-        <v>97928300</v>
+        <v>92697700</v>
       </c>
       <c r="K61" s="3">
         <v>106459000</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>171400</v>
+        <v>162200</v>
       </c>
       <c r="E62" s="3">
-        <v>195700</v>
+        <v>185200</v>
       </c>
       <c r="F62" s="3">
-        <v>518700</v>
+        <v>491000</v>
       </c>
       <c r="G62" s="3">
-        <v>174400</v>
+        <v>165100</v>
       </c>
       <c r="H62" s="3">
-        <v>728700</v>
+        <v>689800</v>
       </c>
       <c r="I62" s="3">
-        <v>2063800</v>
+        <v>1953600</v>
       </c>
       <c r="J62" s="3">
-        <v>946800</v>
+        <v>896200</v>
       </c>
       <c r="K62" s="3">
         <v>1455400</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1616690000</v>
+        <v>1530340000</v>
       </c>
       <c r="E66" s="3">
-        <v>1500570000</v>
+        <v>1420420000</v>
       </c>
       <c r="F66" s="3">
-        <v>1432560000</v>
+        <v>1356050000</v>
       </c>
       <c r="G66" s="3">
-        <v>1366240000</v>
+        <v>1293270000</v>
       </c>
       <c r="H66" s="3">
-        <v>1273080000</v>
+        <v>1205080000</v>
       </c>
       <c r="I66" s="3">
-        <v>1316910000</v>
+        <v>1246570000</v>
       </c>
       <c r="J66" s="3">
-        <v>1295390000</v>
+        <v>1226200000</v>
       </c>
       <c r="K66" s="3">
         <v>1339590000</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>16460100</v>
+        <v>15580900</v>
       </c>
       <c r="E72" s="3">
-        <v>17966200</v>
+        <v>17006600</v>
       </c>
       <c r="F72" s="3">
-        <v>20000200</v>
+        <v>18931900</v>
       </c>
       <c r="G72" s="3">
-        <v>18203200</v>
+        <v>17230900</v>
       </c>
       <c r="H72" s="3">
-        <v>18471300</v>
+        <v>17484700</v>
       </c>
       <c r="I72" s="3">
-        <v>8803400</v>
+        <v>8333200</v>
       </c>
       <c r="J72" s="3">
-        <v>6193300</v>
+        <v>5862500</v>
       </c>
       <c r="K72" s="3">
         <v>5384300</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>60090400</v>
+        <v>56880800</v>
       </c>
       <c r="E76" s="3">
-        <v>60081800</v>
+        <v>56872700</v>
       </c>
       <c r="F76" s="3">
-        <v>61369300</v>
+        <v>58091400</v>
       </c>
       <c r="G76" s="3">
-        <v>57373300</v>
+        <v>54308900</v>
       </c>
       <c r="H76" s="3">
-        <v>58816700</v>
+        <v>55675200</v>
       </c>
       <c r="I76" s="3">
-        <v>59773200</v>
+        <v>56580500</v>
       </c>
       <c r="J76" s="3">
-        <v>55681500</v>
+        <v>52707500</v>
       </c>
       <c r="K76" s="3">
         <v>57071700</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-94400</v>
+        <v>-89400</v>
       </c>
       <c r="E81" s="3">
-        <v>-705800</v>
+        <v>-668100</v>
       </c>
       <c r="F81" s="3">
-        <v>3921100</v>
+        <v>3711700</v>
       </c>
       <c r="G81" s="3">
-        <v>1012300</v>
+        <v>958200</v>
       </c>
       <c r="H81" s="3">
-        <v>569300</v>
+        <v>538900</v>
       </c>
       <c r="I81" s="3">
-        <v>3893100</v>
+        <v>3685100</v>
       </c>
       <c r="J81" s="3">
-        <v>2442800</v>
+        <v>2312400</v>
       </c>
       <c r="K81" s="3">
         <v>6114500</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1610800</v>
+        <v>1524800</v>
       </c>
       <c r="E83" s="3">
-        <v>1539400</v>
+        <v>1457200</v>
       </c>
       <c r="F83" s="3">
-        <v>1561500</v>
+        <v>1478100</v>
       </c>
       <c r="G83" s="3">
-        <v>1642700</v>
+        <v>1555000</v>
       </c>
       <c r="H83" s="3">
-        <v>2393800</v>
+        <v>2265900</v>
       </c>
       <c r="I83" s="3">
-        <v>1207500</v>
+        <v>1143000</v>
       </c>
       <c r="J83" s="3">
-        <v>1153900</v>
+        <v>1092300</v>
       </c>
       <c r="K83" s="3">
         <v>1210800</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>6786600</v>
+        <v>6424100</v>
       </c>
       <c r="E89" s="3">
-        <v>37057100</v>
+        <v>35077800</v>
       </c>
       <c r="F89" s="3">
-        <v>3159400</v>
+        <v>2990700</v>
       </c>
       <c r="G89" s="3">
-        <v>-27236800</v>
+        <v>-25782000</v>
       </c>
       <c r="H89" s="3">
-        <v>4455300</v>
+        <v>4217300</v>
       </c>
       <c r="I89" s="3">
-        <v>-1062600</v>
+        <v>-1005900</v>
       </c>
       <c r="J89" s="3">
-        <v>8177700</v>
+        <v>7740900</v>
       </c>
       <c r="K89" s="3">
         <v>1742700</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1250800</v>
+        <v>-1184000</v>
       </c>
       <c r="E91" s="3">
-        <v>-918200</v>
+        <v>-869200</v>
       </c>
       <c r="F91" s="3">
-        <v>-1425500</v>
+        <v>-1349300</v>
       </c>
       <c r="G91" s="3">
-        <v>-1638000</v>
+        <v>-1550500</v>
       </c>
       <c r="H91" s="3">
-        <v>-1063000</v>
+        <v>-1006200</v>
       </c>
       <c r="I91" s="3">
-        <v>-1969400</v>
+        <v>-1864200</v>
       </c>
       <c r="J91" s="3">
-        <v>-2904400</v>
+        <v>-2749200</v>
       </c>
       <c r="K91" s="3">
         <v>-2801600</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>41723900</v>
+        <v>39495300</v>
       </c>
       <c r="E94" s="3">
-        <v>-33808700</v>
+        <v>-32002900</v>
       </c>
       <c r="F94" s="3">
-        <v>-17613600</v>
+        <v>-16672800</v>
       </c>
       <c r="G94" s="3">
-        <v>-79583100</v>
+        <v>-75332400</v>
       </c>
       <c r="H94" s="3">
-        <v>-45655200</v>
+        <v>-43216700</v>
       </c>
       <c r="I94" s="3">
-        <v>-29571600</v>
+        <v>-27992100</v>
       </c>
       <c r="J94" s="3">
-        <v>-86282600</v>
+        <v>-81674000</v>
       </c>
       <c r="K94" s="3">
         <v>-43101900</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1411700</v>
+        <v>-1336300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1326300</v>
+        <v>-1255500</v>
       </c>
       <c r="F96" s="3">
-        <v>-1284000</v>
+        <v>-1215400</v>
       </c>
       <c r="G96" s="3">
-        <v>-1283200</v>
+        <v>-1214700</v>
       </c>
       <c r="H96" s="3">
-        <v>-1283400</v>
+        <v>-1214800</v>
       </c>
       <c r="I96" s="3">
-        <v>-1283200</v>
+        <v>-1214600</v>
       </c>
       <c r="J96" s="3">
-        <v>-1280800</v>
+        <v>-1212400</v>
       </c>
       <c r="K96" s="3">
         <v>-1408000</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>52321600</v>
+        <v>49527000</v>
       </c>
       <c r="E100" s="3">
-        <v>13422300</v>
+        <v>12705400</v>
       </c>
       <c r="F100" s="3">
-        <v>58583500</v>
+        <v>55454400</v>
       </c>
       <c r="G100" s="3">
-        <v>83285900</v>
+        <v>78837400</v>
       </c>
       <c r="H100" s="3">
-        <v>22972500</v>
+        <v>21745500</v>
       </c>
       <c r="I100" s="3">
-        <v>31358700</v>
+        <v>29683800</v>
       </c>
       <c r="J100" s="3">
-        <v>80002100</v>
+        <v>75729000</v>
       </c>
       <c r="K100" s="3">
         <v>40078300</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>5781300</v>
+        <v>5472500</v>
       </c>
       <c r="E101" s="3">
-        <v>6516200</v>
+        <v>6168200</v>
       </c>
       <c r="F101" s="3">
-        <v>1588000</v>
+        <v>1503200</v>
       </c>
       <c r="G101" s="3">
-        <v>-1549600</v>
+        <v>-1466900</v>
       </c>
       <c r="H101" s="3">
-        <v>1389700</v>
+        <v>1315500</v>
       </c>
       <c r="I101" s="3">
-        <v>-93300</v>
+        <v>-88300</v>
       </c>
       <c r="J101" s="3">
-        <v>-80200</v>
+        <v>-75900</v>
       </c>
       <c r="K101" s="3">
         <v>-202300</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>106613400</v>
+        <v>100918900</v>
       </c>
       <c r="E102" s="3">
-        <v>23186900</v>
+        <v>21948400</v>
       </c>
       <c r="F102" s="3">
-        <v>45717300</v>
+        <v>43275400</v>
       </c>
       <c r="G102" s="3">
-        <v>-25083800</v>
+        <v>-23744000</v>
       </c>
       <c r="H102" s="3">
-        <v>-16837700</v>
+        <v>-15938400</v>
       </c>
       <c r="I102" s="3">
-        <v>631200</v>
+        <v>597400</v>
       </c>
       <c r="J102" s="3">
-        <v>1817100</v>
+        <v>1720000</v>
       </c>
       <c r="K102" s="3">
         <v>-1483200</v>

--- a/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>MFG</t>
   </si>
@@ -656,111 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>21620500</v>
+        <v>40945700</v>
       </c>
       <c r="E8" s="3">
-        <v>9212300</v>
+        <v>24060400</v>
       </c>
       <c r="F8" s="3">
-        <v>9292800</v>
+        <v>10252000</v>
       </c>
       <c r="G8" s="3">
-        <v>13724500</v>
+        <v>10341500</v>
       </c>
       <c r="H8" s="3">
-        <v>14083500</v>
+        <v>15273300</v>
       </c>
       <c r="I8" s="3">
-        <v>11240800</v>
+        <v>15672800</v>
       </c>
       <c r="J8" s="3">
+        <v>12509400</v>
+      </c>
+      <c r="K8" s="3">
         <v>9627600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10816200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10415100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12862100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12867300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12991300</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -800,9 +806,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -842,9 +851,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,26 +1005,29 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-49200</v>
+        <v>-60800</v>
       </c>
       <c r="E15" s="3">
-        <v>-50800</v>
+        <v>-54700</v>
       </c>
       <c r="F15" s="3">
-        <v>-54300</v>
+        <v>-56500</v>
       </c>
       <c r="G15" s="3">
-        <v>-59100</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
+        <v>-60400</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-65800</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>5</v>
@@ -1019,8 +1041,8 @@
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14548900</v>
+        <v>32793500</v>
       </c>
       <c r="E17" s="3">
-        <v>3660300</v>
+        <v>16190800</v>
       </c>
       <c r="F17" s="3">
-        <v>3819800</v>
+        <v>4073400</v>
       </c>
       <c r="G17" s="3">
-        <v>9230900</v>
+        <v>4250900</v>
       </c>
       <c r="H17" s="3">
-        <v>8529800</v>
+        <v>10272600</v>
       </c>
       <c r="I17" s="3">
-        <v>4678600</v>
+        <v>9492500</v>
       </c>
       <c r="J17" s="3">
+        <v>5206600</v>
+      </c>
+      <c r="K17" s="3">
         <v>4203400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3702500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2367200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2489000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4997300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3552000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7071500</v>
+        <v>8152200</v>
       </c>
       <c r="E18" s="3">
-        <v>5552000</v>
+        <v>7869600</v>
       </c>
       <c r="F18" s="3">
-        <v>5473000</v>
+        <v>6178600</v>
       </c>
       <c r="G18" s="3">
-        <v>4493600</v>
+        <v>6090600</v>
       </c>
       <c r="H18" s="3">
-        <v>5553600</v>
+        <v>5000700</v>
       </c>
       <c r="I18" s="3">
-        <v>6562200</v>
+        <v>6180400</v>
       </c>
       <c r="J18" s="3">
+        <v>7302700</v>
+      </c>
+      <c r="K18" s="3">
         <v>5424200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7113800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8047800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10373100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7870000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9439300</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-6630200</v>
+        <v>3371800</v>
       </c>
       <c r="E20" s="3">
-        <v>-7099100</v>
+        <v>-7378500</v>
       </c>
       <c r="F20" s="3">
-        <v>1090500</v>
+        <v>-7900200</v>
       </c>
       <c r="G20" s="3">
-        <v>-3514400</v>
+        <v>1213600</v>
       </c>
       <c r="H20" s="3">
-        <v>-5011000</v>
+        <v>-3911000</v>
       </c>
       <c r="I20" s="3">
-        <v>-1207500</v>
+        <v>-5576500</v>
       </c>
       <c r="J20" s="3">
+        <v>-1343700</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2359400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1513800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1024200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3806900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>132000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3447300</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1963700</v>
+        <v>13094200</v>
       </c>
       <c r="E21" s="3">
-        <v>-92200</v>
+        <v>2176000</v>
       </c>
       <c r="F21" s="3">
-        <v>8039300</v>
+        <v>-111500</v>
       </c>
       <c r="G21" s="3">
-        <v>2531800</v>
+        <v>8937500</v>
       </c>
       <c r="H21" s="3">
-        <v>2805100</v>
+        <v>2808000</v>
       </c>
       <c r="I21" s="3">
-        <v>6496000</v>
+        <v>3107800</v>
       </c>
       <c r="J21" s="3">
+        <v>7222100</v>
+      </c>
+      <c r="K21" s="3">
         <v>4155300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9846700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8120800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8025500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9424400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7491800</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>441300</v>
+        <v>11524100</v>
       </c>
       <c r="E23" s="3">
-        <v>-1547100</v>
+        <v>491100</v>
       </c>
       <c r="F23" s="3">
-        <v>6563500</v>
+        <v>-1721700</v>
       </c>
       <c r="G23" s="3">
-        <v>979300</v>
+        <v>7304200</v>
       </c>
       <c r="H23" s="3">
-        <v>542700</v>
+        <v>1089800</v>
       </c>
       <c r="I23" s="3">
-        <v>5354700</v>
+        <v>603900</v>
       </c>
       <c r="J23" s="3">
+        <v>5959000</v>
+      </c>
+      <c r="K23" s="3">
         <v>3064800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8627500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7023600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6566100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8002000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5992000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>224200</v>
+        <v>3018400</v>
       </c>
       <c r="E24" s="3">
-        <v>-899700</v>
+        <v>249500</v>
       </c>
       <c r="F24" s="3">
-        <v>1344400</v>
+        <v>-1001200</v>
       </c>
       <c r="G24" s="3">
-        <v>301000</v>
+        <v>1496100</v>
       </c>
       <c r="H24" s="3">
-        <v>59600</v>
+        <v>334900</v>
       </c>
       <c r="I24" s="3">
-        <v>1515900</v>
+        <v>66300</v>
       </c>
       <c r="J24" s="3">
+        <v>1687000</v>
+      </c>
+      <c r="K24" s="3">
         <v>582100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2498600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2162400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2044000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>36400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>125500</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>217100</v>
+        <v>8505700</v>
       </c>
       <c r="E26" s="3">
-        <v>-647400</v>
+        <v>241600</v>
       </c>
       <c r="F26" s="3">
-        <v>5219100</v>
+        <v>-720400</v>
       </c>
       <c r="G26" s="3">
-        <v>678300</v>
+        <v>5808100</v>
       </c>
       <c r="H26" s="3">
-        <v>483100</v>
+        <v>754800</v>
       </c>
       <c r="I26" s="3">
-        <v>3838800</v>
+        <v>537600</v>
       </c>
       <c r="J26" s="3">
+        <v>4272000</v>
+      </c>
+      <c r="K26" s="3">
         <v>2482700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6129000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4861200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4522100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7965700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5866600</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-89400</v>
+        <v>6478600</v>
       </c>
       <c r="E27" s="3">
-        <v>-668100</v>
+        <v>-99500</v>
       </c>
       <c r="F27" s="3">
-        <v>3711700</v>
+        <v>-743500</v>
       </c>
       <c r="G27" s="3">
-        <v>958200</v>
+        <v>4130500</v>
       </c>
       <c r="H27" s="3">
-        <v>538900</v>
+        <v>1066400</v>
       </c>
       <c r="I27" s="3">
-        <v>3685100</v>
+        <v>599700</v>
       </c>
       <c r="J27" s="3">
+        <v>4101000</v>
+      </c>
+      <c r="K27" s="3">
         <v>2312400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6114500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4303800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4445300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7839400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5855400</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>6630200</v>
+        <v>-3371800</v>
       </c>
       <c r="E32" s="3">
-        <v>7099100</v>
+        <v>7378500</v>
       </c>
       <c r="F32" s="3">
-        <v>-1090500</v>
+        <v>7900200</v>
       </c>
       <c r="G32" s="3">
-        <v>3514400</v>
+        <v>-1213600</v>
       </c>
       <c r="H32" s="3">
-        <v>5011000</v>
+        <v>3911000</v>
       </c>
       <c r="I32" s="3">
-        <v>1207500</v>
+        <v>5576500</v>
       </c>
       <c r="J32" s="3">
+        <v>1343700</v>
+      </c>
+      <c r="K32" s="3">
         <v>2359400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1513800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1024200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3806900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-132000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3447300</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-89400</v>
+        <v>6478600</v>
       </c>
       <c r="E33" s="3">
-        <v>-668100</v>
+        <v>-99500</v>
       </c>
       <c r="F33" s="3">
-        <v>3711700</v>
+        <v>-743500</v>
       </c>
       <c r="G33" s="3">
-        <v>958200</v>
+        <v>4130500</v>
       </c>
       <c r="H33" s="3">
-        <v>538900</v>
+        <v>1066400</v>
       </c>
       <c r="I33" s="3">
-        <v>3685100</v>
+        <v>599700</v>
       </c>
       <c r="J33" s="3">
+        <v>4101000</v>
+      </c>
+      <c r="K33" s="3">
         <v>2312400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6114500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4303800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4445300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7839400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5855400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-89400</v>
+        <v>6478600</v>
       </c>
       <c r="E35" s="3">
-        <v>-668100</v>
+        <v>-99500</v>
       </c>
       <c r="F35" s="3">
-        <v>3711700</v>
+        <v>-743500</v>
       </c>
       <c r="G35" s="3">
-        <v>958200</v>
+        <v>4130500</v>
       </c>
       <c r="H35" s="3">
-        <v>538900</v>
+        <v>1066400</v>
       </c>
       <c r="I35" s="3">
-        <v>3685100</v>
+        <v>599700</v>
       </c>
       <c r="J35" s="3">
+        <v>4101000</v>
+      </c>
+      <c r="K35" s="3">
         <v>2312400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6114500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4303800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4445300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7839400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5855400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,92 +1986,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>433791000</v>
+        <v>526203000</v>
       </c>
       <c r="E41" s="3">
-        <v>332872000</v>
+        <v>482745000</v>
       </c>
       <c r="F41" s="3">
-        <v>310924000</v>
+        <v>370438000</v>
       </c>
       <c r="G41" s="3">
-        <v>267648000</v>
+        <v>346012000</v>
       </c>
       <c r="H41" s="3">
-        <v>291392000</v>
+        <v>297853000</v>
       </c>
       <c r="I41" s="3">
-        <v>307331000</v>
+        <v>324276000</v>
       </c>
       <c r="J41" s="3">
+        <v>342014000</v>
+      </c>
+      <c r="K41" s="3">
         <v>303605000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>264247000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>206292000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>15339800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11466700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10998300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>320246000</v>
+        <v>457707000</v>
       </c>
       <c r="E42" s="3">
-        <v>286737000</v>
+        <v>356387000</v>
       </c>
       <c r="F42" s="3">
-        <v>287625000</v>
+        <v>319096000</v>
       </c>
       <c r="G42" s="3">
-        <v>330014000</v>
+        <v>320084000</v>
       </c>
       <c r="H42" s="3">
-        <v>251525000</v>
+        <v>367257000</v>
       </c>
       <c r="I42" s="3">
-        <v>254048000</v>
+        <v>279910000</v>
       </c>
       <c r="J42" s="3">
+        <v>282718000</v>
+      </c>
+      <c r="K42" s="3">
         <v>260240000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>322177000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>228831000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>549634000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>550699000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>464937000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2026,9 +2118,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,9 +2163,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2110,9 +2208,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,9 +2253,12 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2183,104 +2287,113 @@
         <v>0</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>2070100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2410200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2725300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3815500</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14058700</v>
+        <v>15885700</v>
       </c>
       <c r="E48" s="3">
-        <v>14509600</v>
+        <v>15645200</v>
       </c>
       <c r="F48" s="3">
-        <v>15458700</v>
+        <v>16147100</v>
       </c>
       <c r="G48" s="3">
-        <v>15754200</v>
+        <v>17203200</v>
       </c>
       <c r="H48" s="3">
-        <v>12128100</v>
+        <v>17532100</v>
       </c>
       <c r="I48" s="3">
-        <v>13501300</v>
+        <v>13496800</v>
       </c>
       <c r="J48" s="3">
+        <v>15024900</v>
+      </c>
+      <c r="K48" s="3">
         <v>13023300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13251900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7643400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12263600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9871600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9988000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>877900</v>
+        <v>1487000</v>
       </c>
       <c r="E49" s="3">
-        <v>897200</v>
+        <v>977000</v>
       </c>
       <c r="F49" s="3">
-        <v>949400</v>
+        <v>998500</v>
       </c>
       <c r="G49" s="3">
-        <v>1006000</v>
+        <v>1056600</v>
       </c>
       <c r="H49" s="3">
-        <v>1080700</v>
+        <v>1119600</v>
       </c>
       <c r="I49" s="3">
-        <v>1146000</v>
+        <v>1202700</v>
       </c>
       <c r="J49" s="3">
+        <v>1275400</v>
+      </c>
+      <c r="K49" s="3">
         <v>1207900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>488500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4662100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>637300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>638400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>686500</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2466500</v>
+        <v>1388800</v>
       </c>
       <c r="E52" s="3">
-        <v>1769300</v>
+        <v>2744800</v>
       </c>
       <c r="F52" s="3">
-        <v>286900</v>
+        <v>1969000</v>
       </c>
       <c r="G52" s="3">
-        <v>872200</v>
+        <v>319300</v>
       </c>
       <c r="H52" s="3">
-        <v>317600</v>
+        <v>970700</v>
       </c>
       <c r="I52" s="3">
-        <v>364200</v>
+        <v>353400</v>
       </c>
       <c r="J52" s="3">
         <v>405300</v>
       </c>
       <c r="K52" s="3">
+        <v>405300</v>
+      </c>
+      <c r="L52" s="3">
         <v>413500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5532500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3662300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5801700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7564000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1587220000</v>
+        <v>1932430000</v>
       </c>
       <c r="E54" s="3">
-        <v>1477290000</v>
+        <v>1766340000</v>
       </c>
       <c r="F54" s="3">
-        <v>1414140000</v>
+        <v>1644010000</v>
       </c>
       <c r="G54" s="3">
-        <v>1347580000</v>
+        <v>1573730000</v>
       </c>
       <c r="H54" s="3">
-        <v>1260760000</v>
+        <v>1499650000</v>
       </c>
       <c r="I54" s="3">
-        <v>1303150000</v>
+        <v>1403040000</v>
       </c>
       <c r="J54" s="3">
+        <v>1450220000</v>
+      </c>
+      <c r="K54" s="3">
         <v>1278910000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1397370000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1344860000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1588320000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1615870000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1503910000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,38 +2654,39 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>14843800</v>
+        <v>11986200</v>
       </c>
       <c r="E57" s="3">
-        <v>12131600</v>
+        <v>16518900</v>
       </c>
       <c r="F57" s="3">
-        <v>19014900</v>
+        <v>13500700</v>
       </c>
       <c r="G57" s="3">
-        <v>16181000</v>
+        <v>21160800</v>
       </c>
       <c r="H57" s="3">
-        <v>19236300</v>
+        <v>18007000</v>
       </c>
       <c r="I57" s="3">
-        <v>11908700</v>
+        <v>21407100</v>
       </c>
       <c r="J57" s="3">
+        <v>13252700</v>
+      </c>
+      <c r="K57" s="3">
         <v>12006800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23974500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2566,20 +2696,23 @@
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>207906000</v>
+      <c r="D58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E58" s="3">
-        <v>195664000</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>5</v>
+        <v>231369000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>217746000</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>5</v>
@@ -2593,8 +2726,8 @@
       <c r="J58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2608,51 +2741,57 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7031400</v>
+        <v>9128500</v>
       </c>
       <c r="E59" s="3">
-        <v>5483100</v>
+        <v>7824900</v>
       </c>
       <c r="F59" s="3">
-        <v>5662300</v>
+        <v>6101900</v>
       </c>
       <c r="G59" s="3">
-        <v>6030100</v>
+        <v>6301300</v>
       </c>
       <c r="H59" s="3">
-        <v>2215400</v>
+        <v>6710600</v>
       </c>
       <c r="I59" s="3">
-        <v>1897300</v>
+        <v>2465400</v>
       </c>
       <c r="J59" s="3">
+        <v>2111400</v>
+      </c>
+      <c r="K59" s="3">
         <v>1804900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2005500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>424500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1963800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1773800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1902700</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,93 +2831,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>95004700</v>
+        <v>115569000</v>
       </c>
       <c r="E61" s="3">
-        <v>80229900</v>
+        <v>105726000</v>
       </c>
       <c r="F61" s="3">
-        <v>74687300</v>
+        <v>89284000</v>
       </c>
       <c r="G61" s="3">
-        <v>66008400</v>
+        <v>83115900</v>
       </c>
       <c r="H61" s="3">
-        <v>73557600</v>
+        <v>73457700</v>
       </c>
       <c r="I61" s="3">
-        <v>82654400</v>
+        <v>81858700</v>
       </c>
       <c r="J61" s="3">
+        <v>91982100</v>
+      </c>
+      <c r="K61" s="3">
         <v>92697700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>106459000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>93656100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>89079600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>79572100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>76494800</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>162200</v>
+        <v>225000</v>
       </c>
       <c r="E62" s="3">
-        <v>185200</v>
+        <v>180500</v>
       </c>
       <c r="F62" s="3">
-        <v>491000</v>
+        <v>206100</v>
       </c>
       <c r="G62" s="3">
-        <v>165100</v>
+        <v>546400</v>
       </c>
       <c r="H62" s="3">
-        <v>689800</v>
+        <v>183700</v>
       </c>
       <c r="I62" s="3">
-        <v>1953600</v>
+        <v>767700</v>
       </c>
       <c r="J62" s="3">
+        <v>2174000</v>
+      </c>
+      <c r="K62" s="3">
         <v>896200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1455400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5104500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>300000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>129300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>143300</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1530340000</v>
+        <v>1861930000</v>
       </c>
       <c r="E66" s="3">
-        <v>1420420000</v>
+        <v>1703040000</v>
       </c>
       <c r="F66" s="3">
-        <v>1356050000</v>
+        <v>1580720000</v>
       </c>
       <c r="G66" s="3">
-        <v>1293270000</v>
+        <v>1509080000</v>
       </c>
       <c r="H66" s="3">
-        <v>1205080000</v>
+        <v>1439220000</v>
       </c>
       <c r="I66" s="3">
-        <v>1246570000</v>
+        <v>1341080000</v>
       </c>
       <c r="J66" s="3">
+        <v>1387250000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1226200000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1339590000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1286980000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1530660000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1564090000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1463490000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3074,23 +3241,26 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>713200</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>1511000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>2826400</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>3411300</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>3709700</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15580900</v>
+        <v>22153700</v>
       </c>
       <c r="E72" s="3">
-        <v>17006600</v>
+        <v>17339300</v>
       </c>
       <c r="F72" s="3">
-        <v>18931900</v>
+        <v>18925800</v>
       </c>
       <c r="G72" s="3">
-        <v>17230900</v>
+        <v>21068400</v>
       </c>
       <c r="H72" s="3">
-        <v>17484700</v>
+        <v>19175500</v>
       </c>
       <c r="I72" s="3">
-        <v>8333200</v>
+        <v>19457900</v>
       </c>
       <c r="J72" s="3">
+        <v>9273600</v>
+      </c>
+      <c r="K72" s="3">
         <v>5862500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5384300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>19661900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4858800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7985800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14519200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>56880800</v>
+        <v>70496400</v>
       </c>
       <c r="E76" s="3">
-        <v>56872700</v>
+        <v>63300000</v>
       </c>
       <c r="F76" s="3">
-        <v>58091400</v>
+        <v>63290900</v>
       </c>
       <c r="G76" s="3">
-        <v>54308900</v>
+        <v>64647200</v>
       </c>
       <c r="H76" s="3">
-        <v>55675200</v>
+        <v>60437800</v>
       </c>
       <c r="I76" s="3">
-        <v>56580500</v>
+        <v>61958300</v>
       </c>
       <c r="J76" s="3">
+        <v>62965800</v>
+      </c>
+      <c r="K76" s="3">
         <v>52707500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>57071700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>56378400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>54835000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>48370900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>36706000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-89400</v>
+        <v>6478600</v>
       </c>
       <c r="E81" s="3">
-        <v>-668100</v>
+        <v>-99500</v>
       </c>
       <c r="F81" s="3">
-        <v>3711700</v>
+        <v>-743500</v>
       </c>
       <c r="G81" s="3">
-        <v>958200</v>
+        <v>4130500</v>
       </c>
       <c r="H81" s="3">
-        <v>538900</v>
+        <v>1066400</v>
       </c>
       <c r="I81" s="3">
-        <v>3685100</v>
+        <v>599700</v>
       </c>
       <c r="J81" s="3">
+        <v>4101000</v>
+      </c>
+      <c r="K81" s="3">
         <v>2312400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6114500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4303800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4445300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7839400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5855400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1524800</v>
+        <v>1581300</v>
       </c>
       <c r="E83" s="3">
-        <v>1457200</v>
+        <v>1696900</v>
       </c>
       <c r="F83" s="3">
-        <v>1478100</v>
+        <v>1621600</v>
       </c>
       <c r="G83" s="3">
-        <v>1555000</v>
+        <v>1644900</v>
       </c>
       <c r="H83" s="3">
-        <v>2265900</v>
+        <v>1730400</v>
       </c>
       <c r="I83" s="3">
-        <v>1143000</v>
+        <v>2521700</v>
       </c>
       <c r="J83" s="3">
+        <v>1272000</v>
+      </c>
+      <c r="K83" s="3">
         <v>1092300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1210800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1139000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1457800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1420800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1498100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>6424100</v>
+        <v>-24569600</v>
       </c>
       <c r="E89" s="3">
-        <v>35077800</v>
+        <v>7149100</v>
       </c>
       <c r="F89" s="3">
-        <v>2990700</v>
+        <v>39036400</v>
       </c>
       <c r="G89" s="3">
-        <v>-25782000</v>
+        <v>3328200</v>
       </c>
       <c r="H89" s="3">
-        <v>4217300</v>
+        <v>-28691600</v>
       </c>
       <c r="I89" s="3">
-        <v>-1005900</v>
+        <v>4693200</v>
       </c>
       <c r="J89" s="3">
+        <v>-1119400</v>
+      </c>
+      <c r="K89" s="3">
         <v>7740900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1742700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>47183700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>53799800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11733800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16176500</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1184000</v>
+        <v>-1821000</v>
       </c>
       <c r="E91" s="3">
-        <v>-869200</v>
+        <v>-1317600</v>
       </c>
       <c r="F91" s="3">
-        <v>-1349300</v>
+        <v>-967300</v>
       </c>
       <c r="G91" s="3">
-        <v>-1550500</v>
+        <v>-1501600</v>
       </c>
       <c r="H91" s="3">
-        <v>-1006200</v>
+        <v>-1725500</v>
       </c>
       <c r="I91" s="3">
-        <v>-1864200</v>
+        <v>-1119800</v>
       </c>
       <c r="J91" s="3">
+        <v>-2074600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2749200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2801600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1533600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4131100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1458700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1577600</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>39495300</v>
+        <v>-26124100</v>
       </c>
       <c r="E94" s="3">
-        <v>-32002900</v>
+        <v>43952500</v>
       </c>
       <c r="F94" s="3">
-        <v>-16672800</v>
+        <v>-35614500</v>
       </c>
       <c r="G94" s="3">
-        <v>-75332400</v>
+        <v>-18554400</v>
       </c>
       <c r="H94" s="3">
-        <v>-43216700</v>
+        <v>-83833900</v>
       </c>
       <c r="I94" s="3">
-        <v>-27992100</v>
+        <v>-48093800</v>
       </c>
       <c r="J94" s="3">
+        <v>-31151100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-81674000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-43101900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>18570300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>3772400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-57149400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16659800</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1336300</v>
+        <v>-1667000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1255500</v>
+        <v>-1487100</v>
       </c>
       <c r="F96" s="3">
-        <v>-1215400</v>
+        <v>-1397200</v>
       </c>
       <c r="G96" s="3">
-        <v>-1214700</v>
+        <v>-1352500</v>
       </c>
       <c r="H96" s="3">
-        <v>-1214800</v>
+        <v>-1351700</v>
       </c>
       <c r="I96" s="3">
-        <v>-1214600</v>
+        <v>-1351900</v>
       </c>
       <c r="J96" s="3">
+        <v>-1351700</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1212400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1408000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1249200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1375600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1378700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1951800</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>49527000</v>
+        <v>81349000</v>
       </c>
       <c r="E100" s="3">
-        <v>12705400</v>
+        <v>55116200</v>
       </c>
       <c r="F100" s="3">
-        <v>55454400</v>
+        <v>14139200</v>
       </c>
       <c r="G100" s="3">
-        <v>78837400</v>
+        <v>61712500</v>
       </c>
       <c r="H100" s="3">
-        <v>21745500</v>
+        <v>87734400</v>
       </c>
       <c r="I100" s="3">
-        <v>29683800</v>
+        <v>24199500</v>
       </c>
       <c r="J100" s="3">
+        <v>33033700</v>
+      </c>
+      <c r="K100" s="3">
         <v>75729000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>40078300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-6405100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-53986900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>69064300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>26811200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>5472500</v>
+        <v>12802100</v>
       </c>
       <c r="E101" s="3">
-        <v>6168200</v>
+        <v>6090100</v>
       </c>
       <c r="F101" s="3">
-        <v>1503200</v>
+        <v>6864300</v>
       </c>
       <c r="G101" s="3">
-        <v>-1466900</v>
+        <v>1672800</v>
       </c>
       <c r="H101" s="3">
-        <v>1315500</v>
+        <v>-1632400</v>
       </c>
       <c r="I101" s="3">
-        <v>-88300</v>
+        <v>1463900</v>
       </c>
       <c r="J101" s="3">
+        <v>-98300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-75900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-202300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>266300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>287800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>287300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-12900</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100918900</v>
+        <v>43457300</v>
       </c>
       <c r="E102" s="3">
-        <v>21948400</v>
+        <v>112307800</v>
       </c>
       <c r="F102" s="3">
-        <v>43275400</v>
+        <v>24425400</v>
       </c>
       <c r="G102" s="3">
-        <v>-23744000</v>
+        <v>48159200</v>
       </c>
       <c r="H102" s="3">
-        <v>-15938400</v>
+        <v>-26423500</v>
       </c>
       <c r="I102" s="3">
-        <v>597400</v>
+        <v>-17737100</v>
       </c>
       <c r="J102" s="3">
+        <v>664900</v>
+      </c>
+      <c r="K102" s="3">
         <v>1720000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1483200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>59615200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3873100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>468400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6037900</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>MFG</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>40945700</v>
+        <v>20641300</v>
       </c>
       <c r="E8" s="3">
-        <v>24060400</v>
+        <v>20906700</v>
       </c>
       <c r="F8" s="3">
-        <v>10252000</v>
+        <v>23106600</v>
       </c>
       <c r="G8" s="3">
-        <v>10341500</v>
+        <v>22199900</v>
       </c>
       <c r="H8" s="3">
-        <v>15273300</v>
+        <v>22413300</v>
       </c>
       <c r="I8" s="3">
-        <v>15672800</v>
+        <v>23063100</v>
       </c>
       <c r="J8" s="3">
-        <v>12509400</v>
+        <v>25570500</v>
       </c>
       <c r="K8" s="3">
         <v>9627600</v>
@@ -815,26 +815,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>20641300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>20906700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>23106600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>22199900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>22413300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>23063100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>25570500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-103500</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>31100</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>505100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-1107000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>141800</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>4475100</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-178900</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-60800</v>
+        <v>1178100</v>
       </c>
       <c r="E15" s="3">
-        <v>-54700</v>
+        <v>1255800</v>
       </c>
       <c r="F15" s="3">
-        <v>-56500</v>
+        <v>1364000</v>
       </c>
       <c r="G15" s="3">
-        <v>-60400</v>
+        <v>1509700</v>
       </c>
       <c r="H15" s="3">
-        <v>-65800</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
+        <v>1456600</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1554700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>1674300</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>32793500</v>
+        <v>14430800</v>
       </c>
       <c r="E17" s="3">
-        <v>16190800</v>
+        <v>15015800</v>
       </c>
       <c r="F17" s="3">
-        <v>4073400</v>
+        <v>17628700</v>
       </c>
       <c r="G17" s="3">
-        <v>4250900</v>
+        <v>17410300</v>
       </c>
       <c r="H17" s="3">
-        <v>10272600</v>
+        <v>16521400</v>
       </c>
       <c r="I17" s="3">
-        <v>9492500</v>
+        <v>17538900</v>
       </c>
       <c r="J17" s="3">
-        <v>5206600</v>
+        <v>18217300</v>
       </c>
       <c r="K17" s="3">
         <v>4203400</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8152200</v>
+        <v>6210500</v>
       </c>
       <c r="E18" s="3">
-        <v>7869600</v>
+        <v>5890900</v>
       </c>
       <c r="F18" s="3">
-        <v>6178600</v>
+        <v>5477900</v>
       </c>
       <c r="G18" s="3">
-        <v>6090600</v>
+        <v>4789600</v>
       </c>
       <c r="H18" s="3">
-        <v>5000700</v>
+        <v>5891900</v>
       </c>
       <c r="I18" s="3">
-        <v>6180400</v>
+        <v>5524200</v>
       </c>
       <c r="J18" s="3">
-        <v>7302700</v>
+        <v>7353200</v>
       </c>
       <c r="K18" s="3">
         <v>5424200</v>
@@ -1184,26 +1184,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>3371800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-7378500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-7900200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1213600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-3911000</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-5576500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1343700</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>-2359400</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13094200</v>
+        <v>7388600</v>
       </c>
       <c r="E21" s="3">
-        <v>2176000</v>
+        <v>7146700</v>
       </c>
       <c r="F21" s="3">
-        <v>-111500</v>
+        <v>6841900</v>
       </c>
       <c r="G21" s="3">
-        <v>8937500</v>
+        <v>6299400</v>
       </c>
       <c r="H21" s="3">
-        <v>2808000</v>
+        <v>7348400</v>
       </c>
       <c r="I21" s="3">
-        <v>3107800</v>
+        <v>7079000</v>
       </c>
       <c r="J21" s="3">
-        <v>7222100</v>
+        <v>9027500</v>
       </c>
       <c r="K21" s="3">
         <v>4155300</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>11524100</v>
+        <v>6314100</v>
       </c>
       <c r="E23" s="3">
-        <v>491100</v>
+        <v>5859800</v>
       </c>
       <c r="F23" s="3">
-        <v>-1721700</v>
+        <v>4972800</v>
       </c>
       <c r="G23" s="3">
-        <v>7304200</v>
+        <v>5896600</v>
       </c>
       <c r="H23" s="3">
-        <v>1089800</v>
+        <v>5750000</v>
       </c>
       <c r="I23" s="3">
-        <v>603900</v>
+        <v>1049200</v>
       </c>
       <c r="J23" s="3">
-        <v>5959000</v>
+        <v>7532200</v>
       </c>
       <c r="K23" s="3">
         <v>3064800</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3018400</v>
+        <v>1796500</v>
       </c>
       <c r="E24" s="3">
-        <v>249500</v>
+        <v>1646200</v>
       </c>
       <c r="F24" s="3">
-        <v>-1001200</v>
+        <v>499800</v>
       </c>
       <c r="G24" s="3">
-        <v>1496100</v>
+        <v>1580400</v>
       </c>
       <c r="H24" s="3">
-        <v>334900</v>
+        <v>1500900</v>
       </c>
       <c r="I24" s="3">
-        <v>66300</v>
+        <v>-22600</v>
       </c>
       <c r="J24" s="3">
-        <v>1687000</v>
+        <v>1804300</v>
       </c>
       <c r="K24" s="3">
         <v>582100</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8505700</v>
+        <v>4517500</v>
       </c>
       <c r="E26" s="3">
-        <v>241600</v>
+        <v>4213600</v>
       </c>
       <c r="F26" s="3">
-        <v>-720400</v>
+        <v>4473100</v>
       </c>
       <c r="G26" s="3">
-        <v>5808100</v>
+        <v>4316300</v>
       </c>
       <c r="H26" s="3">
-        <v>754800</v>
+        <v>4249200</v>
       </c>
       <c r="I26" s="3">
-        <v>537600</v>
+        <v>1071800</v>
       </c>
       <c r="J26" s="3">
-        <v>4272000</v>
+        <v>5727800</v>
       </c>
       <c r="K26" s="3">
         <v>2482700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6478600</v>
+        <v>4489100</v>
       </c>
       <c r="E27" s="3">
-        <v>-99500</v>
+        <v>4179000</v>
       </c>
       <c r="F27" s="3">
-        <v>-743500</v>
+        <v>4368500</v>
       </c>
       <c r="G27" s="3">
-        <v>4130500</v>
+        <v>4258800</v>
       </c>
       <c r="H27" s="3">
-        <v>1066400</v>
+        <v>4168800</v>
       </c>
       <c r="I27" s="3">
-        <v>599700</v>
+        <v>871500</v>
       </c>
       <c r="J27" s="3">
-        <v>4101000</v>
+        <v>5428600</v>
       </c>
       <c r="K27" s="3">
         <v>2312400</v>
@@ -1724,26 +1724,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-3371800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>7378500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>7900200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1213600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>3911000</v>
-      </c>
-      <c r="I32" s="3">
-        <v>5576500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1343700</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>2359400</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6478600</v>
+        <v>4489100</v>
       </c>
       <c r="E33" s="3">
-        <v>-99500</v>
+        <v>4179000</v>
       </c>
       <c r="F33" s="3">
-        <v>-743500</v>
+        <v>4368500</v>
       </c>
       <c r="G33" s="3">
-        <v>4130500</v>
+        <v>4258800</v>
       </c>
       <c r="H33" s="3">
-        <v>1066400</v>
+        <v>4168800</v>
       </c>
       <c r="I33" s="3">
-        <v>599700</v>
+        <v>871500</v>
       </c>
       <c r="J33" s="3">
-        <v>4101000</v>
+        <v>5428600</v>
       </c>
       <c r="K33" s="3">
         <v>2312400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6478600</v>
+        <v>4489100</v>
       </c>
       <c r="E35" s="3">
-        <v>-99500</v>
+        <v>4179000</v>
       </c>
       <c r="F35" s="3">
-        <v>-743500</v>
+        <v>4368500</v>
       </c>
       <c r="G35" s="3">
-        <v>4130500</v>
+        <v>4258800</v>
       </c>
       <c r="H35" s="3">
-        <v>1066400</v>
+        <v>4168800</v>
       </c>
       <c r="I35" s="3">
-        <v>599700</v>
+        <v>871500</v>
       </c>
       <c r="J35" s="3">
-        <v>4101000</v>
+        <v>5428600</v>
       </c>
       <c r="K35" s="3">
         <v>2312400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>526203000</v>
+        <v>470502200</v>
       </c>
       <c r="E41" s="3">
-        <v>482745000</v>
+        <v>495175700</v>
       </c>
       <c r="F41" s="3">
-        <v>370438000</v>
+        <v>412868700</v>
       </c>
       <c r="G41" s="3">
-        <v>346012000</v>
+        <v>433837400</v>
       </c>
       <c r="H41" s="3">
-        <v>297853000</v>
+        <v>381682000</v>
       </c>
       <c r="I41" s="3">
-        <v>324276000</v>
+        <v>407080600</v>
       </c>
       <c r="J41" s="3">
-        <v>342014000</v>
+        <v>449370200</v>
       </c>
       <c r="K41" s="3">
         <v>303605000</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>457707000</v>
+        <v>294345400</v>
       </c>
       <c r="E42" s="3">
-        <v>356387000</v>
+        <v>235325700</v>
       </c>
       <c r="F42" s="3">
-        <v>319096000</v>
+        <v>232627900</v>
       </c>
       <c r="G42" s="3">
-        <v>320084000</v>
+        <v>243407800</v>
       </c>
       <c r="H42" s="3">
-        <v>367257000</v>
+        <v>316661200</v>
       </c>
       <c r="I42" s="3">
-        <v>279910000</v>
+        <v>249249800</v>
       </c>
       <c r="J42" s="3">
-        <v>282718000</v>
+        <v>215983600</v>
       </c>
       <c r="K42" s="3">
         <v>260240000</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>11920800</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>9978000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>10071300</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2127,26 +2127,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>97290400</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>99385100</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>112276200</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>78549500</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>75379100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>72698500</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>72170500</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>877917600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>843735600</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>773383000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>761060300</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>777549800</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>732204500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>740701300</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>280455600</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>309927300</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>396239700</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>424102100</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>349394100</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>294228400</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>347410900</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15885700</v>
+        <v>7533400</v>
       </c>
       <c r="E48" s="3">
-        <v>15645200</v>
+        <v>8318800</v>
       </c>
       <c r="F48" s="3">
-        <v>16147100</v>
+        <v>9025300</v>
       </c>
       <c r="G48" s="3">
-        <v>17203200</v>
+        <v>10266400</v>
       </c>
       <c r="H48" s="3">
-        <v>17532100</v>
+        <v>10256500</v>
       </c>
       <c r="I48" s="3">
-        <v>13496800</v>
+        <v>9358400</v>
       </c>
       <c r="J48" s="3">
-        <v>15024900</v>
+        <v>10462100</v>
       </c>
       <c r="K48" s="3">
         <v>13023300</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1487000</v>
+        <v>4794200</v>
       </c>
       <c r="E49" s="3">
-        <v>977000</v>
+        <v>4308300</v>
       </c>
       <c r="F49" s="3">
-        <v>998500</v>
+        <v>4951600</v>
       </c>
       <c r="G49" s="3">
-        <v>1056600</v>
+        <v>5607900</v>
       </c>
       <c r="H49" s="3">
-        <v>1119600</v>
+        <v>5912000</v>
       </c>
       <c r="I49" s="3">
-        <v>1202700</v>
+        <v>5597200</v>
       </c>
       <c r="J49" s="3">
-        <v>1275400</v>
+        <v>10288700</v>
       </c>
       <c r="K49" s="3">
         <v>1207900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1388800</v>
+        <v>54289000</v>
       </c>
       <c r="E52" s="3">
-        <v>2744800</v>
+        <v>71831300</v>
       </c>
       <c r="F52" s="3">
-        <v>1969000</v>
+        <v>68019800</v>
       </c>
       <c r="G52" s="3">
-        <v>319300</v>
+        <v>81397500</v>
       </c>
       <c r="H52" s="3">
-        <v>970700</v>
+        <v>74319900</v>
       </c>
       <c r="I52" s="3">
-        <v>353400</v>
+        <v>59025600</v>
       </c>
       <c r="J52" s="3">
-        <v>405300</v>
+        <v>69607500</v>
       </c>
       <c r="K52" s="3">
         <v>405300</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1932430000</v>
+        <v>1842399600</v>
       </c>
       <c r="E54" s="3">
-        <v>1766340000</v>
+        <v>1912665000</v>
       </c>
       <c r="F54" s="3">
-        <v>1644010000</v>
+        <v>1952222100</v>
       </c>
       <c r="G54" s="3">
-        <v>1573730000</v>
+        <v>2039676800</v>
       </c>
       <c r="H54" s="3">
-        <v>1499650000</v>
+        <v>1994935800</v>
       </c>
       <c r="I54" s="3">
-        <v>1403040000</v>
+        <v>1812040700</v>
       </c>
       <c r="J54" s="3">
-        <v>1450220000</v>
+        <v>1930495700</v>
       </c>
       <c r="K54" s="3">
         <v>1278910000</v>
@@ -2660,26 +2660,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>11986200</v>
-      </c>
-      <c r="E57" s="3">
-        <v>16518900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>13500700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>21160800</v>
-      </c>
-      <c r="H57" s="3">
-        <v>18007000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>21407100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>13252700</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K57" s="3">
         <v>12006800</v>
@@ -2705,26 +2705,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>5</v>
+      <c r="D58" s="3">
+        <v>308224900</v>
       </c>
       <c r="E58" s="3">
-        <v>231369000</v>
+        <v>250625600</v>
       </c>
       <c r="F58" s="3">
-        <v>217746000</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
+        <v>277862000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>203267300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>195339500</v>
+      </c>
+      <c r="I58" s="3">
+        <v>169471100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>186758600</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9128500</v>
+        <v>164744400</v>
       </c>
       <c r="E59" s="3">
-        <v>7824900</v>
+        <v>174054400</v>
       </c>
       <c r="F59" s="3">
-        <v>6101900</v>
+        <v>107440200</v>
       </c>
       <c r="G59" s="3">
-        <v>6301300</v>
+        <v>133076400</v>
       </c>
       <c r="H59" s="3">
-        <v>6710600</v>
+        <v>145642400</v>
       </c>
       <c r="I59" s="3">
-        <v>2465400</v>
+        <v>129840000</v>
       </c>
       <c r="J59" s="3">
-        <v>2111400</v>
+        <v>130358500</v>
       </c>
       <c r="K59" s="3">
         <v>1804900</v>
@@ -2795,26 +2795,26 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>0</v>
-      </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>115569000</v>
+        <v>115365200</v>
       </c>
       <c r="E61" s="3">
-        <v>105726000</v>
+        <v>116799800</v>
       </c>
       <c r="F61" s="3">
-        <v>89284000</v>
+        <v>143045800</v>
       </c>
       <c r="G61" s="3">
-        <v>83115900</v>
+        <v>179768800</v>
       </c>
       <c r="H61" s="3">
-        <v>73457700</v>
+        <v>151299600</v>
       </c>
       <c r="I61" s="3">
-        <v>81858700</v>
+        <v>126335500</v>
       </c>
       <c r="J61" s="3">
-        <v>91982100</v>
+        <v>176455300</v>
       </c>
       <c r="K61" s="3">
         <v>92697700</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>225000</v>
+        <v>50150100</v>
       </c>
       <c r="E62" s="3">
-        <v>180500</v>
+        <v>63958000</v>
       </c>
       <c r="F62" s="3">
-        <v>206100</v>
+        <v>60854500</v>
       </c>
       <c r="G62" s="3">
-        <v>546400</v>
+        <v>73972000</v>
       </c>
       <c r="H62" s="3">
-        <v>183700</v>
+        <v>77097800</v>
       </c>
       <c r="I62" s="3">
-        <v>767700</v>
+        <v>57758000</v>
       </c>
       <c r="J62" s="3">
-        <v>2174000</v>
+        <v>53723600</v>
       </c>
       <c r="K62" s="3">
         <v>896200</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1861930000</v>
+        <v>1774222500</v>
       </c>
       <c r="E66" s="3">
-        <v>1703040000</v>
+        <v>1843394000</v>
       </c>
       <c r="F66" s="3">
-        <v>1580720000</v>
+        <v>1876452300</v>
       </c>
       <c r="G66" s="3">
-        <v>1509080000</v>
+        <v>1955026800</v>
       </c>
       <c r="H66" s="3">
-        <v>1439220000</v>
+        <v>1914418200</v>
       </c>
       <c r="I66" s="3">
-        <v>1341080000</v>
+        <v>1729069500</v>
       </c>
       <c r="J66" s="3">
-        <v>1387250000</v>
+        <v>1838021300</v>
       </c>
       <c r="K66" s="3">
         <v>1226200000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>22153700</v>
+        <v>36619600</v>
       </c>
       <c r="E72" s="3">
-        <v>17339300</v>
+        <v>38319100</v>
       </c>
       <c r="F72" s="3">
-        <v>18925800</v>
+        <v>39168900</v>
       </c>
       <c r="G72" s="3">
-        <v>21068400</v>
+        <v>39979200</v>
       </c>
       <c r="H72" s="3">
-        <v>19175500</v>
+        <v>38792900</v>
       </c>
       <c r="I72" s="3">
-        <v>19457900</v>
+        <v>35335400</v>
       </c>
       <c r="J72" s="3">
-        <v>9273600</v>
+        <v>37689700</v>
       </c>
       <c r="K72" s="3">
         <v>5862500</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>70496400</v>
+        <v>67650900</v>
       </c>
       <c r="E76" s="3">
-        <v>63300000</v>
+        <v>68705500</v>
       </c>
       <c r="F76" s="3">
-        <v>63290900</v>
+        <v>74752300</v>
       </c>
       <c r="G76" s="3">
-        <v>64647200</v>
+        <v>83693400</v>
       </c>
       <c r="H76" s="3">
-        <v>60437800</v>
+        <v>79498400</v>
       </c>
       <c r="I76" s="3">
-        <v>61958300</v>
+        <v>78959600</v>
       </c>
       <c r="J76" s="3">
-        <v>62965800</v>
+        <v>85372700</v>
       </c>
       <c r="K76" s="3">
         <v>52707500</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6478600</v>
+        <v>4489100</v>
       </c>
       <c r="E81" s="3">
-        <v>-99500</v>
+        <v>4179000</v>
       </c>
       <c r="F81" s="3">
-        <v>-743500</v>
+        <v>4368500</v>
       </c>
       <c r="G81" s="3">
-        <v>4130500</v>
+        <v>4258800</v>
       </c>
       <c r="H81" s="3">
-        <v>1066400</v>
+        <v>4168800</v>
       </c>
       <c r="I81" s="3">
-        <v>599700</v>
+        <v>871500</v>
       </c>
       <c r="J81" s="3">
-        <v>4101000</v>
+        <v>5428600</v>
       </c>
       <c r="K81" s="3">
         <v>2312400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1581300</v>
+        <v>1144900</v>
       </c>
       <c r="E83" s="3">
-        <v>1696900</v>
+        <v>1227400</v>
       </c>
       <c r="F83" s="3">
-        <v>1621600</v>
+        <v>1333200</v>
       </c>
       <c r="G83" s="3">
-        <v>1644900</v>
+        <v>1475900</v>
       </c>
       <c r="H83" s="3">
-        <v>1730400</v>
+        <v>1418800</v>
       </c>
       <c r="I83" s="3">
-        <v>2521700</v>
+        <v>1517900</v>
       </c>
       <c r="J83" s="3">
-        <v>1272000</v>
+        <v>1635100</v>
       </c>
       <c r="K83" s="3">
         <v>1092300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-24569600</v>
+        <v>-1973500</v>
       </c>
       <c r="E89" s="3">
-        <v>7149100</v>
+        <v>17014700</v>
       </c>
       <c r="F89" s="3">
-        <v>39036400</v>
+        <v>19124600</v>
       </c>
       <c r="G89" s="3">
-        <v>3328200</v>
+        <v>111881700</v>
       </c>
       <c r="H89" s="3">
-        <v>-28691600</v>
+        <v>-57596400</v>
       </c>
       <c r="I89" s="3">
-        <v>4693200</v>
+        <v>-49118800</v>
       </c>
       <c r="J89" s="3">
-        <v>-1119400</v>
+        <v>-30173800</v>
       </c>
       <c r="K89" s="3">
         <v>7740900</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1821000</v>
+        <v>-417300</v>
       </c>
       <c r="E91" s="3">
-        <v>-1317600</v>
+        <v>-487800</v>
       </c>
       <c r="F91" s="3">
-        <v>-967300</v>
+        <v>-348300</v>
       </c>
       <c r="G91" s="3">
-        <v>-1501600</v>
+        <v>-971000</v>
       </c>
       <c r="H91" s="3">
-        <v>-1725500</v>
+        <v>-797800</v>
       </c>
       <c r="I91" s="3">
-        <v>-1119800</v>
+        <v>-385400</v>
       </c>
       <c r="J91" s="3">
-        <v>-2074600</v>
+        <v>-545900</v>
       </c>
       <c r="K91" s="3">
         <v>-2749200</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-26124100</v>
+        <v>13105100</v>
       </c>
       <c r="E94" s="3">
-        <v>43952500</v>
+        <v>49691300</v>
       </c>
       <c r="F94" s="3">
-        <v>-35614500</v>
+        <v>-15321000</v>
       </c>
       <c r="G94" s="3">
-        <v>-18554400</v>
+        <v>-88280600</v>
       </c>
       <c r="H94" s="3">
-        <v>-83833900</v>
+        <v>-53981700</v>
       </c>
       <c r="I94" s="3">
-        <v>-48093800</v>
+        <v>49518600</v>
       </c>
       <c r="J94" s="3">
-        <v>-31151100</v>
+        <v>-21808700</v>
       </c>
       <c r="K94" s="3">
         <v>-81674000</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1667000</v>
+        <v>1552300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1487100</v>
+        <v>1575600</v>
       </c>
       <c r="F96" s="3">
-        <v>-1397200</v>
+        <v>1620500</v>
       </c>
       <c r="G96" s="3">
-        <v>-1352500</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-1351700</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-1351900</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-1351700</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-1212400</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>81349000</v>
+        <v>12908600</v>
       </c>
       <c r="E100" s="3">
-        <v>55116200</v>
+        <v>45092100</v>
       </c>
       <c r="F100" s="3">
-        <v>14139200</v>
+        <v>17068900</v>
       </c>
       <c r="G100" s="3">
-        <v>61712500</v>
+        <v>38698800</v>
       </c>
       <c r="H100" s="3">
-        <v>87734400</v>
+        <v>72652300</v>
       </c>
       <c r="I100" s="3">
-        <v>24199500</v>
+        <v>25161300</v>
       </c>
       <c r="J100" s="3">
-        <v>33033700</v>
+        <v>59519600</v>
       </c>
       <c r="K100" s="3">
         <v>75729000</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>12802100</v>
+        <v>11265300</v>
       </c>
       <c r="E101" s="3">
-        <v>6090100</v>
+        <v>6225700</v>
       </c>
       <c r="F101" s="3">
-        <v>6864300</v>
+        <v>5107800</v>
       </c>
       <c r="G101" s="3">
-        <v>1672800</v>
+        <v>2056900</v>
       </c>
       <c r="H101" s="3">
-        <v>-1632400</v>
+        <v>-1884500</v>
       </c>
       <c r="I101" s="3">
-        <v>1463900</v>
+        <v>-294700</v>
       </c>
       <c r="J101" s="3">
-        <v>-98300</v>
+        <v>96100</v>
       </c>
       <c r="K101" s="3">
         <v>-75900</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>43457300</v>
+        <v>35305500</v>
       </c>
       <c r="E102" s="3">
-        <v>112307800</v>
+        <v>118023800</v>
       </c>
       <c r="F102" s="3">
-        <v>24425400</v>
+        <v>25980400</v>
       </c>
       <c r="G102" s="3">
-        <v>48159200</v>
+        <v>64356800</v>
       </c>
       <c r="H102" s="3">
-        <v>-26423500</v>
+        <v>-40810300</v>
       </c>
       <c r="I102" s="3">
-        <v>-17737100</v>
+        <v>25266300</v>
       </c>
       <c r="J102" s="3">
-        <v>664900</v>
+        <v>7633100</v>
       </c>
       <c r="K102" s="3">
         <v>1720000</v>

--- a/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>MFG</t>
   </si>
@@ -656,117 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25936700</v>
+      </c>
+      <c r="E8" s="3">
         <v>20641300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20906700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23106600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22199900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22413300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23063100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>25570500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9627600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10816200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10415100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12862100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>12867300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12991300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,36 +815,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>25936700</v>
+      </c>
+      <c r="E10" s="3">
         <v>20641300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20906700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23106600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>22199900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>22413300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>23063100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>25570500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -854,9 +863,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,36 +979,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E14" s="3">
         <v>-103500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>31100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>505100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1107000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>141800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4475100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-178900</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1008,44 +1027,47 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1375100</v>
+      </c>
+      <c r="E15" s="3">
         <v>1178100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1255800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1364000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1509700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1456600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1554700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1674300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>17977900</v>
+      </c>
+      <c r="E17" s="3">
         <v>14430800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15015800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>17628700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17410300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16521400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17538900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18217300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4203400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3702500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2367200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2489000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4997300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3552000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7958800</v>
+      </c>
+      <c r="E18" s="3">
         <v>6210500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5890900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5477900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4789600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5891900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5524200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7353200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5424200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7113800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8047800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10373100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7870000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9439300</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,8 +1211,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1205,72 +1238,78 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-2359400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1513800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1024200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3806900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>132000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3447300</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9333900</v>
+      </c>
+      <c r="E21" s="3">
         <v>7388600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7146700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6841900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6299400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7348400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7079000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9027500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4155300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9846700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8120800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8025500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9424400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7491800</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1295,8 +1334,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1313,99 +1352,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7947200</v>
+      </c>
+      <c r="E23" s="3">
         <v>6314100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5859800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4972800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5896600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5750000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1049200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7532200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3064800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8627500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7023600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6566100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8002000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5992000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2012800</v>
+      </c>
+      <c r="E24" s="3">
         <v>1796500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1646200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>499800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1580400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1500900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-22600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1804300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>582100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2498600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2162400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2044000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>36400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>125500</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5934400</v>
+      </c>
+      <c r="E26" s="3">
         <v>4517500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4213600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4473100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4316300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4249200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1071800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5727800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2482700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6129000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4861200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4522100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7965700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5866600</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5912800</v>
+      </c>
+      <c r="E27" s="3">
         <v>4489100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4179000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4368500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4258800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4168800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>871500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5428600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2312400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6114500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4303800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4445300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7839400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5855400</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,9 +1784,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1745,72 +1814,78 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>2359400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1513800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1024200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3806900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-132000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3447300</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5912800</v>
+      </c>
+      <c r="E33" s="3">
         <v>4489100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4179000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4368500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4258800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4168800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>871500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5428600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2312400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6114500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4303800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4445300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7839400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5855400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5912800</v>
+      </c>
+      <c r="E35" s="3">
         <v>4489100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4179000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4368500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4258800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4168800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>871500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5428600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2312400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6114500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4303800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4445300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7839400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5855400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,113 +2072,120 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>472282500</v>
+      </c>
+      <c r="E41" s="3">
         <v>470502200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>495175700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>412868700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>433837400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>381682000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>407080600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>449370200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>303605000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>264247000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>206292000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15339800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11466700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10998300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>359576900</v>
+      </c>
+      <c r="E42" s="3">
         <v>294345400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>235325700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>232627900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>243407800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>316661200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>249249800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>215983600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>260240000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>322177000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>228831000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>549634000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>550699000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>464937000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11751200</v>
+      </c>
+      <c r="E43" s="3">
         <v>11920800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9978000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10071300</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2103,8 +2195,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2121,9 +2213,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2148,8 +2243,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2166,36 +2261,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>94432800</v>
+      </c>
+      <c r="E45" s="3">
         <v>97290400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>99385100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>112276200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>78549500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>75379100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>72698500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>72170500</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2211,36 +2309,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>942264000</v>
+      </c>
+      <c r="E46" s="3">
         <v>877917600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>843735600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>773383000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>761060300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>777549800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>732204500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>740701300</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2256,144 +2357,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>255362300</v>
+      </c>
+      <c r="E47" s="3">
         <v>280455600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>309927300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>396239700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>424102100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>349394100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>294228400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>347410900</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>2070100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2410200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2725300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3815500</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7496500</v>
+      </c>
+      <c r="E48" s="3">
         <v>7533400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8318800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9025300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>10266400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>10256500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>9358400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>10462100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13023300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13251900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7643400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12263600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9871600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9988000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5401700</v>
+      </c>
+      <c r="E49" s="3">
         <v>4794200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4308300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4951600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5607900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5912000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5597200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10288700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1207900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>488500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4662100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>637300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>638400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>686500</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51871600</v>
+      </c>
+      <c r="E52" s="3">
         <v>54289000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>71831300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>68019800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>81397500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>74319900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>59025600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>69607500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>405300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>413500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5532500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3662300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5801700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7564000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1891981200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1842399600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1912665000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1952222100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2039676800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1994935800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1812040700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1930495700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1278910000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1397370000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1344860000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1588320000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1615870000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1503910000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,8 +2784,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2681,15 +2811,15 @@
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>12006800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>23974500</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
@@ -2699,38 +2829,41 @@
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>335043700</v>
+      </c>
+      <c r="E58" s="3">
         <v>308224900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>250625600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>277862000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>203267300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>195339500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>169471100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>186758600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2744,54 +2877,60 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>167386300</v>
+      </c>
+      <c r="E59" s="3">
         <v>164744400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>174054400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>107440200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>133076400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>145642400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>129840000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>130358500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1804900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2005500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>424500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1963800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1773800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1902700</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2816,8 +2955,8 @@
       <c r="J60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
+      <c r="K60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -2834,99 +2973,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>112764800</v>
+      </c>
+      <c r="E61" s="3">
         <v>115365200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>116799800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>143045800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>179768800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>151299600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>126335500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>176455300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>92697700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>106459000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>93656100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>89079600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>79572100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>76494800</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>47836900</v>
+      </c>
+      <c r="E62" s="3">
         <v>50150100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>63958000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>60854500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>73972000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>77097800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>57758000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>53723600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>896200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1455400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5104500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>300000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>129300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>143300</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1821704800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1774222500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1843394000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1876452300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1955026800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1914418200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1729069500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1838021300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1226200000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1339590000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1286980000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1530660000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1564090000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1463490000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3244,23 +3411,26 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>713200</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>1511000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>2826400</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>3411300</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>3709700</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>40378400</v>
+      </c>
+      <c r="E72" s="3">
         <v>36619600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>38319100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>39168900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>39979200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>38792900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>35335400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>37689700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5862500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5384300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>19661900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4858800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7985800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-14519200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>69731900</v>
+      </c>
+      <c r="E76" s="3">
         <v>67650900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>68705500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>74752300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>83693400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>79498400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>78959600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>85372700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>52707500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>57071700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>56378400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>54835000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48370900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>36706000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5912800</v>
+      </c>
+      <c r="E81" s="3">
         <v>4489100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4179000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4368500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4258800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4168800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>871500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5428600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2312400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6114500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4303800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4445300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7839400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5855400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1326300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1144900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1227400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1333200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1475900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1418800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1517900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1635100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1092300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1210800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1139000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1457800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1420800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1498100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-38385700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1973500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17014700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>19124600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>111881700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-57596400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-49118800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30173800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7740900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1742700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>47183700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>53799800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11733800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-16176500</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-634000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-417300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-487800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-348300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-971000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-797800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-385400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-545900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2749200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2801600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1533600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4131100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1458700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1577600</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>25329800</v>
+      </c>
+      <c r="E94" s="3">
         <v>13105100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>49691300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15321000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-88280600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-53981700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>49518600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21808700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-81674000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-43101900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>18570300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3772400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-57149400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-16659800</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,23 +4453,24 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2032900</v>
+      </c>
+      <c r="E96" s="3">
         <v>1552300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1575600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1620500</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -4248,26 +4481,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-1212400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1408000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1249200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1375600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1378700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1951800</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10873900</v>
+      </c>
+      <c r="E100" s="3">
         <v>12908600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>45092100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17068900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>38698800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>72652300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>25161300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>59519600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>75729000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>40078300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6405100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-53986900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>69064300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>26811200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-772700</v>
+      </c>
+      <c r="E101" s="3">
         <v>11265300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6225700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5107800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2056900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1884500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-294700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>96100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-75900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-202300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>266300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>287800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>287300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2954700</v>
+      </c>
+      <c r="E102" s="3">
         <v>35305500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>118023800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>25980400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>64356800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-40810300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25266300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7633100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1720000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1483200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>59615200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3873100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>468400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6037900</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>MFG</t>
   </si>
@@ -729,7 +729,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>25936700</v>
+        <v>26036000</v>
       </c>
       <c r="E8" s="3">
         <v>20641300</v>
@@ -825,7 +825,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>25936700</v>
+        <v>26036000</v>
       </c>
       <c r="E10" s="3">
         <v>20641300</v>
@@ -1102,7 +1102,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>17977900</v>
+        <v>18077200</v>
       </c>
       <c r="E17" s="3">
         <v>14430800</v>
@@ -2079,7 +2079,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>472282500</v>
+        <v>484033800</v>
       </c>
       <c r="E41" s="3">
         <v>470502200</v>
@@ -2127,7 +2127,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>359576900</v>
+        <v>350102600</v>
       </c>
       <c r="E42" s="3">
         <v>294345400</v>
@@ -2174,8 +2174,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>11751200</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E43" s="3">
         <v>11920800</v>
@@ -2271,7 +2271,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>94432800</v>
+        <v>80549500</v>
       </c>
       <c r="E45" s="3">
         <v>97290400</v>
@@ -2319,7 +2319,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>942264000</v>
+        <v>918906400</v>
       </c>
       <c r="E46" s="3">
         <v>877917600</v>
@@ -2607,7 +2607,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>51871600</v>
+        <v>75229100</v>
       </c>
       <c r="E52" s="3">
         <v>54289000</v>
@@ -2839,7 +2839,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>335043700</v>
+        <v>293834100</v>
       </c>
       <c r="E58" s="3">
         <v>308224900</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>167386300</v>
+        <v>161036000</v>
       </c>
       <c r="E59" s="3">
         <v>164744400</v>
@@ -2983,7 +2983,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>112764800</v>
+        <v>129829100</v>
       </c>
       <c r="E61" s="3">
         <v>115365200</v>
@@ -3031,7 +3031,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>47836900</v>
+        <v>78332600</v>
       </c>
       <c r="E62" s="3">
         <v>50150100</v>
@@ -4460,7 +4460,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>2032900</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>1552300</v>

--- a/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MFG_YR_FIN.xlsx
@@ -4460,7 +4460,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>2032900</v>
       </c>
       <c r="E96" s="3">
         <v>1552300</v>
@@ -4472,13 +4472,13 @@
         <v>1620500</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>1722400</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>1769400</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>1718400</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
